--- a/src/attributions/attributions_saliency_traj_461.xlsx
+++ b/src/attributions/attributions_saliency_traj_461.xlsx
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.000848695170134306</v>
+        <v>8.433084092152043e-12</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01699518784880638</v>
+        <v>2.115231600985368e-11</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003455341211520135</v>
+        <v>9.396116697202306e-12</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005400278139859438</v>
+        <v>1.929613413498288e-11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00451749749481678</v>
+        <v>2.573540165695665e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00838061235845089</v>
+        <v>3.284950783610796e-11</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001949849538505077</v>
+        <v>2.083667266505884e-11</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01123142056167126</v>
+        <v>2.350410014187454e-12</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01992828771471977</v>
+        <v>7.675226773584676e-12</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0045323446393013</v>
+        <v>6.449210089576329e-12</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01163334771990776</v>
+        <v>3.811188864499826e-11</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004038217011839151</v>
+        <v>3.575492115923118e-12</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01351839117705822</v>
+        <v>2.079109454045103e-11</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0001336317509412766</v>
+        <v>4.081603457994909e-11</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004718202631920576</v>
+        <v>5.365788022237972e-11</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003675890620797873</v>
+        <v>1.389553142688849e-11</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.006520871073007584</v>
+        <v>1.718519944404751e-11</v>
       </c>
       <c r="R2" t="n">
-        <v>0.02080735191702843</v>
+        <v>1.581037037401423e-11</v>
       </c>
       <c r="S2" t="n">
-        <v>0.002429133048281074</v>
+        <v>5.805147161586088e-12</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000865609385073185</v>
+        <v>6.260603147012489e-12</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004016713239252567</v>
+        <v>2.834520812511343e-12</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0002130864886566997</v>
+        <v>1.92813872507136e-11</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003201317973434925</v>
+        <v>5.981890330297723e-12</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0072020273655653</v>
+        <v>2.422679244717951e-12</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0001943573006428778</v>
+        <v>8.898215497765705e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00306343100965023</v>
+        <v>1.340065558519399e-11</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003276703646406531</v>
+        <v>6.969360852315809e-12</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004770838655531406</v>
+        <v>3.633715073628196e-12</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.002176379319280386</v>
+        <v>9.089937136330661e-12</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0134718269109726</v>
+        <v>1.25082860735759e-11</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.001087144715711474</v>
+        <v>3.778811291654804e-11</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.001975623657926917</v>
+        <v>2.368178222966755e-11</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.001736472244374454</v>
+        <v>6.595771671891182e-12</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.003142287954688072</v>
+        <v>4.792472408504667e-12</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.0002380769001320004</v>
+        <v>1.393554282386189e-11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0002925023436546326</v>
+        <v>1.422432831243992e-11</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.001236520591191947</v>
+        <v>7.175530135350439e-12</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.001058223773725331</v>
+        <v>7.021798940909374e-12</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0014925766736269</v>
+        <v>1.864705004989142e-12</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.001085140975192189</v>
+        <v>5.730760484212727e-12</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.002367688342928886</v>
+        <v>9.047971573361568e-12</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.002809495199471712</v>
+        <v>1.328434584557669e-11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.001216090051457286</v>
+        <v>1.320678982841272e-11</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.0004880197811871767</v>
+        <v>6.364577267992111e-12</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.002188948448747396</v>
+        <v>5.96208759445771e-12</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0006352955242618918</v>
+        <v>4.16376612008551e-12</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.01963754184544086</v>
+        <v>5.958904203406945e-11</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.0028310043271631</v>
+        <v>8.417433416951781e-13</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.0007346943602897227</v>
+        <v>3.26301659303585e-12</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.01695477031171322</v>
+        <v>1.260762154398076e-11</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.0001308675855398178</v>
+        <v>4.784719061928788e-12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.003875984344631433</v>
+        <v>9.458714193832929e-12</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.005373409483581781</v>
+        <v>1.619226974725052e-11</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.002657397650182247</v>
+        <v>9.115094963541015e-12</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.003279108321294188</v>
+        <v>3.444628480023249e-12</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.003679679241031408</v>
+        <v>2.230364677668906e-11</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.001761261140927672</v>
+        <v>8.259387965225962e-12</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.002372334944084287</v>
+        <v>1.745434352606878e-11</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.003308593761175871</v>
+        <v>2.96127046495176e-11</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.0105659170076251</v>
+        <v>2.51450561761235e-11</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.001406264957040548</v>
+        <v>4.606894293129882e-12</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.00587119534611702</v>
+        <v>1.43239725636235e-11</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.01976854912936687</v>
+        <v>3.789237586898642e-12</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.002190220169723034</v>
+        <v>6.989115015898495e-12</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.001491679693572223</v>
+        <v>1.282722539297509e-11</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.002807086333632469</v>
+        <v>2.000694315079654e-12</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0007783723995089531</v>
+        <v>4.899867837859784e-12</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.01605900563299656</v>
+        <v>1.478767629181643e-11</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.004641854669898748</v>
+        <v>9.689834871984271e-12</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.004465834703296423</v>
+        <v>2.618674027621282e-11</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.002064395695924759</v>
+        <v>7.443289040676149e-12</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.005792056210339069</v>
+        <v>8.760098549331907e-12</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.001125227892771363</v>
+        <v>2.557172138969999e-12</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.01117145363241434</v>
+        <v>3.006229987168041e-11</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.005375232081860304</v>
+        <v>3.568660774874721e-12</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.0003815028467215598</v>
+        <v>1.776183367052653e-14</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.004696278367191553</v>
+        <v>2.127897337500517e-11</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.002921134233474731</v>
+        <v>3.634982072286963e-12</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.816340075805783e-05</v>
+        <v>1.024252991449481e-11</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.004522373899817467</v>
+        <v>1.392124349824941e-11</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.004554739221930504</v>
+        <v>8.017224037426551e-12</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0002966079628095031</v>
+        <v>2.547855372861396e-12</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.003065576544031501</v>
+        <v>1.035511693753266e-11</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.002196721732616425</v>
+        <v>1.561479678197086e-12</v>
       </c>
       <c r="CG2" t="n">
-        <v>1.279346906812862e-05</v>
+        <v>1.032694069147411e-11</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.001139524974860251</v>
+        <v>7.972806442824165e-12</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.0008077343227341771</v>
+        <v>8.352224294128074e-12</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.00165006029419601</v>
+        <v>1.019244411093467e-11</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.002300258260220289</v>
+        <v>2.391933222670173e-12</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.004927261732518673</v>
+        <v>2.058660967391157e-12</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.005512170027941465</v>
+        <v>1.695414468538825e-11</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.003613208886235952</v>
+        <v>3.325532210718407e-11</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.00059257831890136</v>
+        <v>3.329787617509239e-12</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.004233408719301224</v>
+        <v>2.60987967348747e-11</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.007262402214109898</v>
+        <v>3.772637410803803e-11</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.004445908591151237</v>
+        <v>5.33678049668973e-12</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.001468003494665027</v>
+        <v>4.526400521759344e-12</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.005679672583937645</v>
+        <v>1.100690111971447e-11</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.002956100273877382</v>
+        <v>8.613954168013027e-12</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0001919250062201172</v>
+        <v>5.814267903941905e-12</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.003479067934677005</v>
+        <v>1.030631222725953e-11</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.00199178559705615</v>
+        <v>8.932824640574266e-13</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.0003826686588581651</v>
+        <v>7.290622099087596e-12</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.0005404283874668181</v>
+        <v>5.75977330066757e-12</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0002775603206828237</v>
+        <v>9.560376795780812e-12</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.00160993030294776</v>
+        <v>5.115069826033825e-12</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.001772768795490265</v>
+        <v>4.392497650329563e-12</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.003600460477173328</v>
+        <v>4.805573907556981e-12</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.003850133158266544</v>
+        <v>7.343972652229525e-12</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.003077454632148147</v>
+        <v>2.179612827030164e-13</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.003585134167224169</v>
+        <v>7.582477397696796e-13</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.004228009376674891</v>
+        <v>7.566543745729515e-12</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.00024061618023552</v>
+        <v>1.379131834775005e-12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.001390125835314393</v>
+        <v>3.140135504051123e-12</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.002448962535709143</v>
+        <v>1.669165153317387e-11</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.00977378711104393</v>
+        <v>2.803856105626501e-12</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.0004087728448212147</v>
+        <v>1.898583287113231e-12</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.002480305964127183</v>
+        <v>8.817935531063581e-13</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.0006908533396199346</v>
+        <v>4.835579853201821e-12</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.001427284674718976</v>
+        <v>4.410313694108714e-12</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.002736268565058708</v>
+        <v>1.745034672318013e-11</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.00240408768877387</v>
+        <v>1.897986628973669e-11</v>
       </c>
       <c r="DS2" t="n">
-        <v>1.559368683956563e-05</v>
+        <v>1.012378375575551e-11</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.0006115087307989597</v>
+        <v>2.21679532369512e-11</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.001422250759787858</v>
+        <v>1.412096915093253e-11</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.005527012050151825</v>
+        <v>5.541672155884303e-12</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.0007240652921609581</v>
+        <v>7.075184188520822e-12</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.008833080530166626</v>
+        <v>1.333050943935765e-11</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.001501248218119144</v>
+        <v>9.615043136679269e-12</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.0003374111838638783</v>
+        <v>3.189398181321912e-12</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.0001868241088232026</v>
+        <v>5.645773779039409e-12</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.004378765821456909</v>
+        <v>5.590940904687258e-12</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.001706305425614119</v>
+        <v>8.64261353455964e-13</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.003831557463854551</v>
+        <v>2.446903964170577e-11</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.003111409489065409</v>
+        <v>2.470710051480363e-12</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.0008955059456638992</v>
+        <v>8.780598644009263e-12</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.001168111572042108</v>
+        <v>7.211733380613206e-14</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.004175703506916761</v>
+        <v>1.247787246791421e-12</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.002558029955253005</v>
+        <v>8.266271347978638e-12</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.001255203504115343</v>
+        <v>2.048157433584552e-12</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.001064015552401543</v>
+        <v>3.82163311413164e-12</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.002066645538434386</v>
+        <v>4.323502059838669e-12</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.002730776555836201</v>
+        <v>9.502515961601343e-12</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.00583824934437871</v>
+        <v>3.092576542074177e-12</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.001252326881513</v>
+        <v>4.049485139573372e-12</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.003386191790923476</v>
+        <v>8.920758012495589e-13</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.002921825041994452</v>
+        <v>2.202802556246913e-13</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.00235736882314086</v>
+        <v>5.53908655054336e-12</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.003645251039415598</v>
+        <v>7.631594141355169e-12</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.002866610419005156</v>
+        <v>5.156517140364469e-12</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.001788652152754366</v>
+        <v>6.747679129857909e-13</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.0001412449637427926</v>
+        <v>1.250034884631157e-11</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.002355560194700956</v>
+        <v>1.89929860033855e-11</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.001241073361597955</v>
+        <v>3.994781935801051e-12</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.004099379293620586</v>
+        <v>1.206385425583933e-11</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.00161367654800415</v>
+        <v>1.079653944371928e-12</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.0006892146775498986</v>
+        <v>7.970173132587632e-12</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.000382789468858391</v>
+        <v>6.335196690160361e-12</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.001177702681161463</v>
+        <v>4.960417493427016e-12</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.001670343335717916</v>
+        <v>6.12130094876373e-12</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.001971426652744412</v>
+        <v>4.371662754021344e-12</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.00393423717468977</v>
+        <v>1.723506320300272e-12</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.0009486942435614765</v>
+        <v>3.848852660193192e-12</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.001628604019060731</v>
+        <v>6.163423937888268e-12</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.001443251734599471</v>
+        <v>1.878602525276496e-12</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.001363741117529571</v>
+        <v>8.745297021273135e-12</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.005436539184302092</v>
+        <v>6.523634497185293e-12</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.0004355862038210034</v>
+        <v>1.88310868634578e-12</v>
       </c>
       <c r="FM2" t="n">
-        <v>7.481678039766848e-05</v>
+        <v>4.385903966397375e-12</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.00150955212302506</v>
+        <v>1.841118923984197e-11</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.001099042245186865</v>
+        <v>1.734485168339295e-12</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.002845840994268656</v>
+        <v>1.27811476680062e-11</v>
       </c>
       <c r="FQ2" t="n">
-        <v>6.025051698088646e-05</v>
+        <v>2.082628340616122e-11</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.002225721953436732</v>
+        <v>4.147477066646088e-12</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.001422400586307049</v>
+        <v>1.140231485619037e-11</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.004590244498103857</v>
+        <v>2.178050274859178e-12</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.005011183675378561</v>
+        <v>6.321888325333536e-12</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.0059928884729743</v>
+        <v>1.325194641521588e-11</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.002797897206619382</v>
+        <v>1.209713926253464e-11</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.002586619229987264</v>
+        <v>4.598300906710762e-12</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.002898128237575293</v>
+        <v>6.558579634247108e-13</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.003929711878299713</v>
+        <v>1.454813049542314e-12</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.003220546059310436</v>
+        <v>4.154727777094802e-14</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.003707418218255043</v>
+        <v>8.337820017745301e-12</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.002180218230932951</v>
+        <v>2.720492451105394e-12</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.002641170984134078</v>
+        <v>1.303810878705569e-11</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.002352111041545868</v>
+        <v>1.124416879050294e-11</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.003171676304191351</v>
+        <v>2.127369461146777e-13</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.001659970497712493</v>
+        <v>3.234267237708921e-12</v>
       </c>
     </row>
     <row r="3">
@@ -2706,571 +2706,571 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.002357218414545059</v>
+        <v>5.292303484338845e-09</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0250789187848568</v>
+        <v>2.211410610186704e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00536264106631279</v>
+        <v>2.016038225249872e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007083365228027105</v>
+        <v>4.784894702680731e-11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01080801151692867</v>
+        <v>3.452535146664104e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004895397461950779</v>
+        <v>4.832065858551005e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01598475128412247</v>
+        <v>7.209771002436582e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001562823890708387</v>
+        <v>8.127933881496574e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0150898415595293</v>
+        <v>2.778397512059883e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00583379715681076</v>
+        <v>4.666067088265891e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02556196600198746</v>
+        <v>1.651865533247587e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003834041533991694</v>
+        <v>2.565800460985201e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.005348735488951206</v>
+        <v>4.922071639157366e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01152643281966448</v>
+        <v>5.156299831554634e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001365152769722044</v>
+        <v>2.104670659974772e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01146227493882179</v>
+        <v>1.029225948911971e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.402473031310365e-05</v>
+        <v>6.740245694913938e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01202919147908688</v>
+        <v>8.011616925429621e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002837816486135125</v>
+        <v>1.705115049155381e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007131736259907484</v>
+        <v>1.222126289057712e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001837912714108825</v>
+        <v>1.406421867855556e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007116431836038828</v>
+        <v>3.148366234384525e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01553485821932554</v>
+        <v>1.114735415086443e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>0.006461964920163155</v>
+        <v>1.34437572185675e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002598225604742765</v>
+        <v>2.334154647343212e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00124713743571192</v>
+        <v>3.959103045403367e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0002804309478960931</v>
+        <v>2.354164641005241e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.005346022546291351</v>
+        <v>8.094735548525023e-09</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.003583833109587431</v>
+        <v>7.345408281622667e-09</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.009246004745364189</v>
+        <v>2.023391898475779e-09</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.003349423874169588</v>
+        <v>9.132528067112844e-10</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.00182342273183167</v>
+        <v>3.012332383534044e-09</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.003105364507064223</v>
+        <v>1.471274102549103e-09</v>
       </c>
       <c r="AH5" t="n">
-        <v>8.75664409250021e-06</v>
+        <v>6.087465531656733e-10</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.005876821931451559</v>
+        <v>4.674607367860517e-09</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.002975451527163386</v>
+        <v>2.872304394330172e-09</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.004960902500897646</v>
+        <v>7.020747316843767e-10</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0004017857136204839</v>
+        <v>1.548616790358892e-10</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.120362089248374e-05</v>
+        <v>2.046988134551952e-10</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.001566234626807272</v>
+        <v>3.631545286708615e-09</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0003143702051602304</v>
+        <v>5.438706707217023e-10</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.001769895083270967</v>
+        <v>2.314911595746594e-10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.001452010939829051</v>
+        <v>2.952247113441331e-09</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.002228434896096587</v>
+        <v>3.053521879792243e-09</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.002077797893434763</v>
+        <v>7.416792735526201e-10</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.004463003948330879</v>
+        <v>6.790331630313062e-10</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.01510955952107906</v>
+        <v>4.756324667454237e-09</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.006590314675122499</v>
+        <v>1.561409890271648e-09</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.01128195598721504</v>
+        <v>3.165148143580154e-10</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.004698439966887236</v>
+        <v>3.8046210626419e-09</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.004539478570222855</v>
+        <v>3.897425049359526e-09</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.01473221648484468</v>
+        <v>1.805811389310463e-09</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0003427015617489815</v>
+        <v>5.166373995280082e-09</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.00833355076611042</v>
+        <v>1.552967199280886e-09</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0007239587139338255</v>
+        <v>8.732541356692991e-10</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.01532383635640144</v>
+        <v>4.813990317487082e-10</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.008715890347957611</v>
+        <v>5.641949130108515e-10</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0006425746250897646</v>
+        <v>1.504504631988368e-09</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.00204737507738173</v>
+        <v>4.480051440935995e-09</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.004817122593522072</v>
+        <v>3.654269997710458e-09</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.001738902181386948</v>
+        <v>5.786693346720995e-10</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.002581567037850618</v>
+        <v>5.645565126499719e-10</v>
       </c>
       <c r="BK5" t="n">
-        <v>9.35862772166729e-07</v>
+        <v>9.737332717918434e-09</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0009721911046653986</v>
+        <v>2.063983206568309e-09</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.000107677944470197</v>
+        <v>3.71934927301254e-09</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.00431261770427227</v>
+        <v>1.617883826909861e-09</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.003318753559142351</v>
+        <v>1.120646242469547e-09</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.01658634841442108</v>
+        <v>2.950704791615522e-09</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.004227907862514257</v>
+        <v>1.277588923542794e-09</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.00155238201841712</v>
+        <v>4.778602402666365e-09</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.01313728280365467</v>
+        <v>1.01695152299186e-10</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0005717701860703528</v>
+        <v>7.96749499709648e-10</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.001790022011846304</v>
+        <v>2.029101331402217e-09</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.003072956576943398</v>
+        <v>1.737453736438965e-09</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.003459354862570763</v>
+        <v>3.360649536432447e-10</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.008691543713212013</v>
+        <v>1.336987409672474e-09</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.006812163628637791</v>
+        <v>3.162972994630309e-09</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.001204916043207049</v>
+        <v>2.189637804406175e-09</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.00818986352533102</v>
+        <v>4.914999074401294e-09</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.007404533214867115</v>
+        <v>1.375875857689834e-09</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.005489258095622063</v>
+        <v>9.860634531122514e-10</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.001103441580198705</v>
+        <v>6.708225086526909e-10</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.005254806485027075</v>
+        <v>1.450444431227993e-09</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0004172497137915343</v>
+        <v>1.266373783614938e-09</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.00253288634121418</v>
+        <v>9.238811105038991e-11</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.00222875690087676</v>
+        <v>6.064667656957567e-10</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.001188398920930922</v>
+        <v>3.56337633011794e-11</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.001864114892669022</v>
+        <v>1.597946996945154e-09</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.001847096835263073</v>
+        <v>1.124917520245461e-10</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0007103553507477045</v>
+        <v>3.630975242696621e-10</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.006660892628133297</v>
+        <v>4.36831459893483e-09</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.01017860975116491</v>
+        <v>7.424686199186681e-09</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.001065725111402571</v>
+        <v>4.100192185774176e-09</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.01283121295273304</v>
+        <v>3.675432846961257e-09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.01596505753695965</v>
+        <v>2.815802035982529e-09</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.000385162653401494</v>
+        <v>1.4779826251754e-09</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.005137971602380276</v>
+        <v>1.25354226998553e-09</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.003064239397644997</v>
+        <v>4.242846074475892e-09</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.006887761875987053</v>
+        <v>4.173827505837835e-09</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.001614891225472093</v>
+        <v>3.580468421748861e-10</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.003980584442615509</v>
+        <v>4.437919476352192e-10</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0009968032827600837</v>
+        <v>1.259432447220377e-09</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0006032936507835984</v>
+        <v>2.308479518653428e-10</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0002328143746126443</v>
+        <v>2.108775931652929e-10</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.002494040410965681</v>
+        <v>5.804292602107353e-10</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.00236907135695219</v>
+        <v>8.664604589370128e-10</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.003839151933789253</v>
+        <v>2.736938453651305e-10</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.000599678372964263</v>
+        <v>9.497976849459633e-10</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.006974185816943645</v>
+        <v>1.658697734718828e-09</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.001345352036878467</v>
+        <v>1.924283177245911e-09</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.00361899146810174</v>
+        <v>6.29495655601886e-09</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.01104521565139294</v>
+        <v>8.380814264796754e-09</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.005511103197932243</v>
+        <v>3.131033654568682e-09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.001342928037047386</v>
+        <v>2.371855156724223e-09</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.001893692533485591</v>
+        <v>5.162504201905449e-09</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.005267403088510036</v>
+        <v>2.005370314250854e-09</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.008537194691598415</v>
+        <v>4.012097876149312e-10</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.006371427793055773</v>
+        <v>9.796294331287925e-11</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.003393546910956502</v>
+        <v>2.913072894017432e-09</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.004275928251445293</v>
+        <v>2.793685838220483e-10</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.001216687494888902</v>
+        <v>5.860780749600281e-10</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.001400416949763894</v>
+        <v>5.104789035925705e-09</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.001499950885772705</v>
+        <v>1.507739710859823e-09</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0003385883173905313</v>
+        <v>4.093934080628969e-09</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0022414515260607</v>
+        <v>2.275146737673595e-09</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.007102330215275288</v>
+        <v>2.495666340252001e-09</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0007177777588367462</v>
+        <v>2.635998641586923e-10</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.01072590239346027</v>
+        <v>7.039925975504957e-09</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.002109428867697716</v>
+        <v>1.075926792104553e-09</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.005511300172656775</v>
+        <v>4.185988444760369e-09</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.001804794184863567</v>
+        <v>4.378554852024763e-09</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.003009157488122582</v>
+        <v>2.269465726456588e-09</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.002005710965022445</v>
+        <v>3.316367847006063e-09</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.002634749747812748</v>
+        <v>1.886453215860229e-09</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.003198338206857443</v>
+        <v>5.522872381646948e-09</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.000111449473479297</v>
+        <v>1.860381626528351e-09</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.003737647086381912</v>
+        <v>3.503378254166023e-09</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0009207574184983969</v>
+        <v>1.398326454626897e-09</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.001188983558677137</v>
+        <v>1.212442479747722e-09</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.001171254785731435</v>
+        <v>5.744935083207281e-10</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0008374840253964067</v>
+        <v>3.216839017383677e-09</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.006340098567306995</v>
+        <v>7.727409823132803e-10</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.000141074531711638</v>
+        <v>1.842454799838578e-10</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0006771682528778911</v>
+        <v>2.219906758416101e-10</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.005018319468945265</v>
+        <v>1.091403523112433e-09</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0002580941654741764</v>
+        <v>9.385532351302572e-10</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.002177834045141935</v>
+        <v>1.109373592989016e-09</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0008517643436789513</v>
+        <v>1.468087651446126e-09</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0009176675230264664</v>
+        <v>1.109347391725635e-09</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.007799354381859303</v>
+        <v>2.666428411401967e-09</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.002422762103378773</v>
+        <v>2.99852809249046e-09</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0007931051659397781</v>
+        <v>2.289185951909189e-09</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.002367472276091576</v>
+        <v>1.432015339641879e-10</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.002537879627197981</v>
+        <v>1.278083971989474e-09</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.005002467893064022</v>
+        <v>1.278176231522821e-09</v>
       </c>
       <c r="EZ5" t="n">
-        <v>3.111595287919044e-05</v>
+        <v>1.254093384694954e-09</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.002744076540693641</v>
+        <v>8.035155873997724e-10</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0003715840866789222</v>
+        <v>6.982736611149676e-10</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0005929061444476247</v>
+        <v>7.557776071642763e-10</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.00120706157758832</v>
+        <v>1.069776489615037e-09</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.003739482257515192</v>
+        <v>3.982475460517776e-10</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0006824582233093679</v>
+        <v>1.084004885854029e-09</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.003634133609011769</v>
+        <v>3.397385706094269e-09</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.003670235630124807</v>
+        <v>4.776354867175314e-09</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.001648747129365802</v>
+        <v>1.376199709746118e-09</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0004116702475585043</v>
+        <v>6.020418608088107e-10</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0009772115154191852</v>
+        <v>7.766385867746806e-10</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.008165465667843819</v>
+        <v>1.422488571378722e-09</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0001528889988549054</v>
+        <v>1.627622259192663e-09</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.003831215435639024</v>
+        <v>3.699688999603268e-09</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.007693709339946508</v>
+        <v>6.717079781282109e-09</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.001540385186672211</v>
+        <v>2.083202055302991e-09</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.005277904681861401</v>
+        <v>9.879895124242921e-09</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.003749845549464226</v>
+        <v>5.429434679626866e-12</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.002586295362561941</v>
+        <v>3.84783360729557e-09</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.002317422302439809</v>
+        <v>6.903337013142163e-09</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.003587067360058427</v>
+        <v>3.174344787026939e-09</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0003515697026159614</v>
+        <v>6.277108166585776e-09</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.005188064184039831</v>
+        <v>1.096611690343252e-08</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.005189147777855396</v>
+        <v>4.935368780323302e-10</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.00530257448554039</v>
+        <v>4.454543400811417e-10</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0009483658941462636</v>
+        <v>2.756473382881097e-10</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.006085477769374847</v>
+        <v>3.837786088922712e-09</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.003381658345460892</v>
+        <v>4.384874241480929e-09</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.0053829001262784</v>
+        <v>4.410694920409242e-09</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.003150199539959431</v>
+        <v>2.978667312802941e-09</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.006712780799716711</v>
+        <v>2.805790044746459e-10</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.0140641238540411</v>
+        <v>3.202173193272984e-09</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.002385326661169529</v>
+        <v>1.584281150712741e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3844,1140 +3844,1140 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0008397030178457499</v>
+        <v>0.04534253850579262</v>
       </c>
       <c r="B7" t="n">
-        <v>0.04116532951593399</v>
+        <v>0.08760654926300049</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002962269820272923</v>
+        <v>0.08209327608346939</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02461879327893257</v>
+        <v>0.1308435201644897</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006922326982021332</v>
+        <v>0.02516220510005951</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003919671289622784</v>
+        <v>0.01268516294658184</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005468917079269886</v>
+        <v>0.1184761524200439</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006671834737062454</v>
+        <v>0.1172823533415794</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00748015008866787</v>
+        <v>0.1056126207113266</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001922374125570059</v>
+        <v>0.04471708089113235</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03401608392596245</v>
+        <v>0.1266633868217468</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001937785651534796</v>
+        <v>0.04207230731844902</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0231635682284832</v>
+        <v>0.1755348742008209</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01061009801924229</v>
+        <v>0.003362245857715607</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005098205059766769</v>
+        <v>0.02202831208705902</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001194368931464851</v>
+        <v>0.04709932208061218</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.004865713883191347</v>
+        <v>0.2375158071517944</v>
       </c>
       <c r="R7" t="n">
-        <v>0.000659802695736289</v>
+        <v>0.09739162027835846</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004088824498467147</v>
+        <v>0.02270086854696274</v>
       </c>
       <c r="T7" t="n">
-        <v>0.009109055623412132</v>
+        <v>0.08021456748247147</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003320876508951187</v>
+        <v>0.08047715574502945</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0006857002736069262</v>
+        <v>0.002460695803165436</v>
       </c>
       <c r="W7" t="n">
-        <v>0.005278480239212513</v>
+        <v>0.01801267638802528</v>
       </c>
       <c r="X7" t="n">
-        <v>0.008309447206556797</v>
+        <v>0.04653725028038025</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.004429657012224197</v>
+        <v>0.009228534996509552</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002033688593655825</v>
+        <v>0.02790829353034496</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.004539903253316879</v>
+        <v>0.02460101060569286</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.00038527837023139</v>
+        <v>0.03194107487797737</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.008512599393725395</v>
+        <v>0.06476905196905136</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.001164115383289754</v>
+        <v>0.009492386132478714</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.001166247762739658</v>
+        <v>0.164650559425354</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.003384861862286925</v>
+        <v>0.07954403012990952</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.00537502346560359</v>
+        <v>0.1408590972423553</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.003681193571537733</v>
+        <v>0.04431045800447464</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.005069904029369354</v>
+        <v>0.01480644103139639</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001118947635404766</v>
+        <v>0.02061116509139538</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.002143842866644263</v>
+        <v>0.001444760710000992</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.003092329017817974</v>
+        <v>0.1321913748979568</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0008379297214560211</v>
+        <v>0.1104787588119507</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0008110083290375769</v>
+        <v>0.02829098328948021</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.003457758110016584</v>
+        <v>0.08310973644256592</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.003035231027752161</v>
+        <v>0.02218716964125633</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.004486724268645048</v>
+        <v>0.01108099706470966</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.003460749750956893</v>
+        <v>0.003651731880381703</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0001770675007719547</v>
+        <v>0.0131639251485467</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.003486268687993288</v>
+        <v>0.002166720107197762</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.02501200325787067</v>
+        <v>0.1674420684576035</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.003054838394746184</v>
+        <v>0.05021002516150475</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.003681904170662165</v>
+        <v>0.07734797149896622</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.002650921931490302</v>
+        <v>0.02221870422363281</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.004961167462170124</v>
+        <v>0.05957433208823204</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.001915266737341881</v>
+        <v>0.000895895529538393</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.007776396349072456</v>
+        <v>0.04433941841125488</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.002824535127729177</v>
+        <v>0.01677411049604416</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.003033175598829985</v>
+        <v>0.03374040871858597</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.006887911818921566</v>
+        <v>0.1947610080242157</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.009861803613603115</v>
+        <v>0.08814094215631485</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.004502235911786556</v>
+        <v>0.08080098032951355</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.01280563976615667</v>
+        <v>0.1191825866699219</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0005837989738211036</v>
+        <v>0.05304812267422676</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.002071660943329334</v>
+        <v>0.02858531102538109</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.005671077873557806</v>
+        <v>0.1334081292152405</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0001632688654353842</v>
+        <v>0.1243328526616096</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.004186626058071852</v>
+        <v>0.007784782443195581</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0005812245653942227</v>
+        <v>0.06254786252975464</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.001802150742150843</v>
+        <v>0.02719613164663315</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0006760418764315546</v>
+        <v>0.03761510923504829</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.006643841043114662</v>
+        <v>0.04966041073203087</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.006865056231617928</v>
+        <v>0.06599880009889603</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0005428852746263146</v>
+        <v>0.02514833025634289</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.005871315486729145</v>
+        <v>0.05726482719182968</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.003335342044010758</v>
+        <v>0.01420504692941904</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.00117089506238699</v>
+        <v>0.02845140546560287</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.01374298147857189</v>
+        <v>0.204539567232132</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.002038429956883192</v>
+        <v>0.05623620748519897</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.00189185980707407</v>
+        <v>0.04604580998420715</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.004435781389474869</v>
+        <v>0.005865312181413174</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.003867164952680469</v>
+        <v>0.05627256259322166</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.002399120945483446</v>
+        <v>0.0123184397816658</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.002175802597776055</v>
+        <v>0.09884163737297058</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.001463020220398903</v>
+        <v>0.04637811705470085</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0007985633565112948</v>
+        <v>0.00621626153588295</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.00768715888261795</v>
+        <v>0.03297858312726021</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.001642914954572916</v>
+        <v>0.02156567946076393</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.002259455155581236</v>
+        <v>0.04916498064994812</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.002278886269778013</v>
+        <v>0.02635074406862259</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0004760377341881394</v>
+        <v>0.01559255085885525</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.001205498818308115</v>
+        <v>0.0181419663131237</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0007500046631321311</v>
+        <v>0.0299471877515316</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.001126948511227965</v>
+        <v>0.0186585932970047</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.007731138728559017</v>
+        <v>0.04648566991090775</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.001744172303006053</v>
+        <v>0.01398082543164492</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0006874140235595405</v>
+        <v>0.04346783831715584</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.009519370272755623</v>
+        <v>0.1518705785274506</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.008629569783806801</v>
+        <v>0.1012490689754486</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.005188599228858948</v>
+        <v>0.02268033660948277</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.007584713399410248</v>
+        <v>0.0400640033185482</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.00729651004076004</v>
+        <v>0.0575903132557869</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.001162048429250717</v>
+        <v>0.06955403834581375</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0003726661088876426</v>
+        <v>0.006064771674573421</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.006589555181562901</v>
+        <v>0.03555154055356979</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.003218553960323334</v>
+        <v>0.02673538960516453</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.003939865622669458</v>
+        <v>0.05415603891015053</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.002306799404323101</v>
+        <v>0.008994844742119312</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.001138261053711176</v>
+        <v>0.01123170740902424</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.002276917221024632</v>
+        <v>0.01459410134702921</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0001559761585667729</v>
+        <v>0.03045677579939365</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0007368024671450257</v>
+        <v>0.01350831799209118</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.002269024727866054</v>
+        <v>0.001298985444009304</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.01160058192908764</v>
+        <v>0.09387475997209549</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.003703270573168993</v>
+        <v>0.108056478202343</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.004945200402289629</v>
+        <v>0.02741039916872978</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.004556517116725445</v>
+        <v>0.00256047397851944</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.00024042883887887</v>
+        <v>0.08576178550720215</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.001856960239820182</v>
+        <v>0.04450857266783714</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0002645181957632303</v>
+        <v>0.09413732588291168</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.003463695757091045</v>
+        <v>0.04553087800741196</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.001105025177821517</v>
+        <v>0.02061367221176624</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.002491693245247006</v>
+        <v>0.01374705508351326</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0003231113369110972</v>
+        <v>0.01133996155112982</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0006019981228746474</v>
+        <v>0.01544138602912426</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.004642530810087919</v>
+        <v>0.03118075989186764</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.002703559352084994</v>
+        <v>0.006777228321880102</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.0005654714768752456</v>
+        <v>0.0134858749806881</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.003691761055961251</v>
+        <v>0.04402716457843781</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.001883123535662889</v>
+        <v>0.08559292554855347</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0008640199666842818</v>
+        <v>0.009483302012085915</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.00223112222738564</v>
+        <v>0.03715867549180984</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.005950434133410454</v>
+        <v>0.0608961209654808</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.00186916021630168</v>
+        <v>0.02733666263520718</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.001876098569482565</v>
+        <v>0.06099771335721016</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0005466491566039622</v>
+        <v>0.04708904027938843</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.001723230117931962</v>
+        <v>0.01196802966296673</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0009652371518313885</v>
+        <v>0.005827135872095823</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.0003726808354258537</v>
+        <v>0.05915399640798569</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.001975164515897632</v>
+        <v>0.02359340898692608</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.004644209053367376</v>
+        <v>0.0214350987225771</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.003090775804594159</v>
+        <v>0.02901777625083923</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.002790187252685428</v>
+        <v>0.04272693768143654</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.003614593530073762</v>
+        <v>0.01800801604986191</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.002128514694049954</v>
+        <v>0.0587184876203537</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.001669031567871571</v>
+        <v>0.001840316224843264</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0008712008129805326</v>
+        <v>0.01504944637417793</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.001083414768800139</v>
+        <v>0.006242651492357254</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.001187494955956936</v>
+        <v>0.01282262708991766</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.007049338426440954</v>
+        <v>0.07354950904846191</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.004396565724164248</v>
+        <v>0.01187628880143166</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.002645475789904594</v>
+        <v>0.02019687741994858</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0007842757040634751</v>
+        <v>0.005588213447481394</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.001877750037238002</v>
+        <v>0.02892509289085865</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.004335667937994003</v>
+        <v>0.03811990842223167</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.00231289304792881</v>
+        <v>0.01055082306265831</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0007519690552726388</v>
+        <v>0.03590255603194237</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0003996418963652104</v>
+        <v>0.004053739365190268</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.007218373473733664</v>
+        <v>0.04299334436655045</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.001155382720753551</v>
+        <v>0.004174599424004555</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.003446134738624096</v>
+        <v>0.05350261926651001</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.003121385583654046</v>
+        <v>0.01841418445110321</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.002081087557598948</v>
+        <v>0.004243068862706423</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.001508462009951472</v>
+        <v>0.01433963049203157</v>
       </c>
       <c r="FE7" t="n">
-        <v>7.240351988002658e-05</v>
+        <v>0.02030552551150322</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.00133050512522459</v>
+        <v>0.0163164995610714</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0003903991309925914</v>
+        <v>0.01140958163887262</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.0004818849265575409</v>
+        <v>0.03540175408124924</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.005525819957256317</v>
+        <v>0.01974176429212093</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.002338521648198366</v>
+        <v>0.05173512920737267</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.0002753951121121645</v>
+        <v>0.04091769456863403</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.001807180466130376</v>
+        <v>0.03916426748037338</v>
       </c>
       <c r="FM7" t="n">
-        <v>1.896807225421071e-05</v>
+        <v>0.002324135508388281</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.0009960840689018369</v>
+        <v>0.008783770725131035</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.001243320526555181</v>
+        <v>0.07796406745910645</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.001363040413707495</v>
+        <v>0.05024638772010803</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.004037275910377502</v>
+        <v>0.0513223297894001</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.004112886730581522</v>
+        <v>0.04228406026959419</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.0008201852906495333</v>
+        <v>0.0199897326529026</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.002164495876058936</v>
+        <v>0.1258150786161423</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.001150249503552914</v>
+        <v>0.02609250321984291</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.001522153150290251</v>
+        <v>0.04126700386404991</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.00126672419719398</v>
+        <v>0.001565002836287022</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.005512621253728867</v>
+        <v>0.008387397974729538</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.004047730471938848</v>
+        <v>0.002774556167423725</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.001946828560903668</v>
+        <v>0.09694936871528625</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.001108104828745127</v>
+        <v>0.03456384688615799</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.002358084777370095</v>
+        <v>0.01228880509734154</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.002380826976150274</v>
+        <v>0.09035088866949081</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.007760751061141491</v>
+        <v>0.03254133835434914</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.01226278021931648</v>
+        <v>0.07334350794553757</v>
       </c>
       <c r="GF7" t="n">
-        <v>9.58458986133337e-06</v>
+        <v>0.0242721363902092</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.004507705569267273</v>
+        <v>0.001395131926983595</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0005279644974507391</v>
+        <v>0.3311951756477356</v>
       </c>
       <c r="B8" t="n">
-        <v>0.004641965962946415</v>
+        <v>0.6809126138687134</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003719680826179683</v>
+        <v>0.1483118385076523</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002615858800709248</v>
+        <v>0.01955246925354004</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0006411425420083106</v>
+        <v>0.04116382449865341</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003049335442483425</v>
+        <v>0.4609462022781372</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0002275373262818903</v>
+        <v>0.03142312914133072</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001128808595240116</v>
+        <v>0.09265046566724777</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001983977854251862</v>
+        <v>0.1708561778068542</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001317000482231379</v>
+        <v>0.1800857186317444</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003634718712419271</v>
+        <v>0.9087477922439575</v>
       </c>
       <c r="L8" t="n">
-        <v>7.877628377173096e-05</v>
+        <v>0.07767348736524582</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002270909026265144</v>
+        <v>0.1665544211864471</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0005676209693774581</v>
+        <v>0.1969578564167023</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003294663038104773</v>
+        <v>0.4841143190860748</v>
       </c>
       <c r="P8" t="n">
-        <v>3.552119596861303e-05</v>
+        <v>0.08009299635887146</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.013699850067496e-05</v>
+        <v>0.1473322212696075</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0001628011232241988</v>
+        <v>0.190478578209877</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003434094251133502</v>
+        <v>0.004815472289919853</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0005968123441562057</v>
+        <v>0.2335646152496338</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0002793626626953483</v>
+        <v>0.008956514298915863</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0004589718882925808</v>
+        <v>0.2728308141231537</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0003170397831127048</v>
+        <v>0.1540340185165405</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0002529027406126261</v>
+        <v>0.09284017235040665</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0005559294950217009</v>
+        <v>0.02925366163253784</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0003816807002294809</v>
+        <v>0.1461402624845505</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0005161968292668462</v>
+        <v>0.0222559068351984</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.111049929633737e-05</v>
+        <v>0.03906989842653275</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0004669170302804559</v>
+        <v>0.1830198913812637</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0001381863548886031</v>
+        <v>0.07018311321735382</v>
       </c>
       <c r="AE8" t="n">
-        <v>9.953335393220186e-05</v>
+        <v>0.3242537975311279</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0002574693644419312</v>
+        <v>0.4016348123550415</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0001129430893342942</v>
+        <v>0.1109249740839005</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.000292125012492761</v>
+        <v>0.07377751171588898</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0003471757809165865</v>
+        <v>0.2686545848846436</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0001778975420165807</v>
+        <v>0.01965365000069141</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0003876706468872726</v>
+        <v>0.04789190739393234</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0007073576562106609</v>
+        <v>0.3179486989974976</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0002378243370912969</v>
+        <v>0.06613579392433167</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.000162358905072324</v>
+        <v>0.119910717010498</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0002625499619171023</v>
+        <v>0.1483456939458847</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0006144003127701581</v>
+        <v>0.1385266184806824</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.730880027636886e-05</v>
+        <v>0.07301868498325348</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0002984227903652936</v>
+        <v>0.2414668798446655</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0006464352481998503</v>
+        <v>0.06956513226032257</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0002591327647678554</v>
+        <v>0.1376876980066299</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.002803265582770109</v>
+        <v>0.9945179224014282</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0002589748473837972</v>
+        <v>0.05723093822598457</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.000155842921230942</v>
+        <v>0.006874613463878632</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0001150950120063499</v>
+        <v>0.1089732572436333</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.001721942215226591</v>
+        <v>0.5591868162155151</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.067767152562737e-05</v>
+        <v>0.03217358887195587</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.0008120027487166226</v>
+        <v>0.02357827126979828</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0009830347262322903</v>
+        <v>0.06273841112852097</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0006582615897059441</v>
+        <v>0.1251490712165833</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0009157107560895383</v>
+        <v>0.3023167550563812</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001236689509823918</v>
+        <v>0.09326530992984772</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.0008712075650691986</v>
+        <v>0.1548425853252411</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001286422717384994</v>
+        <v>0.2808570861816406</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0008727812673896551</v>
+        <v>0.04528263956308365</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0003313567722216249</v>
+        <v>0.1602019667625427</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.0009454297251068056</v>
+        <v>0.06357464194297791</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.870137490797788e-05</v>
+        <v>0.09474973380565643</v>
       </c>
       <c r="BL8" t="n">
-        <v>4.6958914026618e-05</v>
+        <v>0.1025441437959671</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0005269658286124468</v>
+        <v>0.06544013321399689</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0005964016891084611</v>
+        <v>0.01396553125232458</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0004220058035571128</v>
+        <v>0.04918162524700165</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0001773686963133514</v>
+        <v>0.09984040260314941</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.69925143988803e-05</v>
+        <v>0.1005373224616051</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0005405209958553314</v>
+        <v>0.09852012991905212</v>
       </c>
       <c r="BS8" t="n">
-        <v>2.732628490775824e-05</v>
+        <v>0.02273494750261307</v>
       </c>
       <c r="BT8" t="n">
-        <v>4.164405982010067e-05</v>
+        <v>0.08121664822101593</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0002253556885989383</v>
+        <v>0.06603020429611206</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001470269518904388</v>
+        <v>0.6511059999465942</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.0006944254273548722</v>
+        <v>0.00208842009305954</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0005500702536664903</v>
+        <v>0.1194265186786652</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0004479584167711437</v>
+        <v>0.1044113337993622</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0005657218280248344</v>
+        <v>0.3492690622806549</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.000354098214302212</v>
+        <v>0.1035465002059937</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0003815007512457669</v>
+        <v>0.05991493910551071</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0007281802245415747</v>
+        <v>0.05524937808513641</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.982525231549516e-05</v>
+        <v>0.006750989705324173</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0007451214478351176</v>
+        <v>0.2734062969684601</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0006042708409950137</v>
+        <v>0.01592195965349674</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0003969973186030984</v>
+        <v>0.0180199071764946</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0003180036146659404</v>
+        <v>0.03901403397321701</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0005370143335312605</v>
+        <v>0.1427487730979919</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.000283469504211098</v>
+        <v>0.06975062191486359</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0001923406380228698</v>
+        <v>0.02985728904604912</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0004067411937285215</v>
+        <v>0.01005216129124165</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0004948102287016809</v>
+        <v>0.2424550503492355</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.119144872063771e-05</v>
+        <v>0.5025418400764465</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0002590435615275055</v>
+        <v>0.001344013959169388</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0005508318427018821</v>
+        <v>0.3658868074417114</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.421629687887616e-05</v>
+        <v>0.3636512160301208</v>
       </c>
       <c r="CR8" t="n">
-        <v>3.445304173510522e-06</v>
+        <v>0.3453898727893829</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0006992629496380687</v>
+        <v>0.04305902123451233</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0006437019910663366</v>
+        <v>0.01264425180852413</v>
       </c>
       <c r="CU8" t="n">
-        <v>7.533024472650141e-05</v>
+        <v>0.06783367693424225</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.918945392593741e-05</v>
+        <v>0.03666894882917404</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.0006823812727816403</v>
+        <v>0.2456871122121811</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0005811474402435124</v>
+        <v>0.01924216374754906</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0006029350915923715</v>
+        <v>0.0409553125500679</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0002959035628009588</v>
+        <v>0.03207936510443687</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0005920544499531388</v>
+        <v>0.1316213756799698</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0002629442315082997</v>
+        <v>0.01740217208862305</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0004464432131499052</v>
+        <v>0.05338376015424728</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0002790909493342042</v>
+        <v>0.02166171371936798</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0004085146065335721</v>
+        <v>0.09571298956871033</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0006083043990656734</v>
+        <v>0.04752647876739502</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0001707381306914613</v>
+        <v>0.03718044236302376</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.001560425036586821</v>
+        <v>0.02046255022287369</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0002225122007075697</v>
+        <v>0.2081632018089294</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0002002742403419688</v>
+        <v>0.07968015223741531</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.0005309757543727756</v>
+        <v>0.1203762143850327</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.0006492817774415016</v>
+        <v>0.2049442231655121</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0002684684586711228</v>
+        <v>0.01703723147511482</v>
       </c>
       <c r="DN8" t="n">
-        <v>9.653418965172023e-05</v>
+        <v>0.02052591368556023</v>
       </c>
       <c r="DO8" t="n">
-        <v>5.149026765138842e-05</v>
+        <v>0.1201071515679359</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0003918933216482401</v>
+        <v>0.04009239375591278</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0004205965669825673</v>
+        <v>0.1341097205877304</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0001808057131711394</v>
+        <v>0.05493779107928276</v>
       </c>
       <c r="DS8" t="n">
-        <v>2.803131064865738e-05</v>
+        <v>0.02490254119038582</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0002222053444711491</v>
+        <v>0.06856337189674377</v>
       </c>
       <c r="DU8" t="n">
-        <v>3.183255466865376e-05</v>
+        <v>0.2323078066110611</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0006480683805420995</v>
+        <v>0.02302392944693565</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0001726077753119171</v>
+        <v>0.1066614240407944</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0003862614976242185</v>
+        <v>0.1229259073734283</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0006986494990997016</v>
+        <v>0.07436862587928772</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.00015686520782765</v>
+        <v>0.0345732569694519</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0001497291814303026</v>
+        <v>0.03732794523239136</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0003117186715826392</v>
+        <v>0.1459617167711258</v>
       </c>
       <c r="EC8" t="n">
-        <v>4.622715641744435e-05</v>
+        <v>0.0712774395942688</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0002148611820302904</v>
+        <v>0.04551560804247856</v>
       </c>
       <c r="EE8" t="n">
-        <v>3.763575659831986e-05</v>
+        <v>0.05822613835334778</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.000277186743915081</v>
+        <v>0.01069971732795238</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0005623374017886817</v>
+        <v>0.02024410478770733</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0004347270005382597</v>
+        <v>0.03723594918847084</v>
       </c>
       <c r="EI8" t="n">
-        <v>6.053844117559493e-05</v>
+        <v>0.06274767965078354</v>
       </c>
       <c r="EJ8" t="n">
-        <v>2.223518822574988e-05</v>
+        <v>0.05578425526618958</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.000432371161878109</v>
+        <v>0.00820560660213232</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.0004524853720795363</v>
+        <v>0.001338718226179481</v>
       </c>
       <c r="EM8" t="n">
-        <v>6.50214496999979e-05</v>
+        <v>0.007598850410431623</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0001109620206989348</v>
+        <v>0.002724011428654194</v>
       </c>
       <c r="EO8" t="n">
-        <v>3.671050944831222e-05</v>
+        <v>0.04423881322145462</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0003276235074736178</v>
+        <v>0.08364208042621613</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0006463825120590627</v>
+        <v>0.01583694852888584</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.0003645308897830546</v>
+        <v>0.02431975305080414</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0004280184220988303</v>
+        <v>0.07123561948537827</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0005477269296534359</v>
+        <v>0.02463387325406075</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0005756999016739428</v>
+        <v>0.002366276457905769</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0007689045160077512</v>
+        <v>0.02367807552218437</v>
       </c>
       <c r="EW8" t="n">
-        <v>1.340011658612639e-05</v>
+        <v>0.01844475232064724</v>
       </c>
       <c r="EX8" t="n">
-        <v>7.810499664628878e-05</v>
+        <v>0.01117600873112679</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0006603148067370057</v>
+        <v>0.2809558510780334</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.000463963981019333</v>
+        <v>0.01594661734998226</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.0004893958102911711</v>
+        <v>0.04185917973518372</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0003576381714083254</v>
+        <v>0.007326159626245499</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0004751897940877825</v>
+        <v>0.1336211115121841</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0004471491847652942</v>
+        <v>0.09074604511260986</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0002757795446086675</v>
+        <v>0.05219008401036263</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.0004557870561257005</v>
+        <v>0.03849469870328903</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0001342295145150274</v>
+        <v>0.04048138484358788</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0002936063974630088</v>
+        <v>0.263171374797821</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.0005689691170118749</v>
+        <v>0.03487537801265717</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.0007776783313602209</v>
+        <v>0.2353638410568237</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0002000446256715804</v>
+        <v>0.09487536549568176</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.0004201097181066871</v>
+        <v>0.180080235004425</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.0002619382576085627</v>
+        <v>0.1259868890047073</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.0001811681722756475</v>
+        <v>0.3150106370449066</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.0003445346374064684</v>
+        <v>0.01383407041430473</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.0001638571120565757</v>
+        <v>0.160654217004776</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.0008518734248355031</v>
+        <v>0.4719101190567017</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.0004043095686938614</v>
+        <v>0.06591121852397919</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.0007402619812637568</v>
+        <v>0.2881427407264709</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0006607837276533246</v>
+        <v>0.1210156828165054</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0003527514054439962</v>
+        <v>0.2195242792367935</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.0004435709561221302</v>
+        <v>0.1306697875261307</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.0002555041864980012</v>
+        <v>0.01640728861093521</v>
       </c>
       <c r="FX8" t="n">
-        <v>6.323309207800776e-05</v>
+        <v>0.02598369307816029</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.0008897926891222596</v>
+        <v>0.03934849798679352</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.0001447375252610072</v>
+        <v>0.107210174202919</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.0001152881668531336</v>
+        <v>0.0001229718327522278</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0001756677665980533</v>
+        <v>0.1312943398952484</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.0002072721108561382</v>
+        <v>0.0137712312862277</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.0004259771085344255</v>
+        <v>0.002437547314912081</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.002173937857151031</v>
+        <v>0.1078323721885681</v>
       </c>
       <c r="GF8" t="n">
-        <v>8.270973921753466e-06</v>
+        <v>0.1303744465112686</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0003575239679776132</v>
+        <v>0.1390595734119415</v>
       </c>
     </row>
     <row r="9">
@@ -5551,2278 +5551,2278 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.5047942399978638</v>
+        <v>1.022965989250224e-06</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7496424317359924</v>
+        <v>1.973241705854889e-05</v>
       </c>
       <c r="C10" t="n">
-        <v>0.03613877296447754</v>
+        <v>9.049646905623376e-06</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1561054140329361</v>
+        <v>1.2781147233909e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3249167501926422</v>
+        <v>1.464929664507508e-05</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0140921613201499</v>
+        <v>1.825720573833678e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1422117203474045</v>
+        <v>7.910076419648249e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>1.113240122795105</v>
+        <v>4.592016466631321e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1645239442586899</v>
+        <v>1.843980044213822e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4269214570522308</v>
+        <v>1.801994949346408e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4793554842472076</v>
+        <v>2.517717803129926e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1029751300811768</v>
+        <v>1.833392343542073e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02499586343765259</v>
+        <v>3.333130734972656e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.469526618719101</v>
+        <v>2.904578104789834e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001066615805029869</v>
+        <v>2.02045284822816e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.04942452907562256</v>
+        <v>2.55938466580119e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.276350617408752</v>
+        <v>2.135086469934322e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3319461643695831</v>
+        <v>1.761554813128896e-08</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1139047220349312</v>
+        <v>1.363594856229611e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>0.240998849272728</v>
+        <v>2.34764302149415e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02180877886712551</v>
+        <v>7.049325176922139e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1088759452104568</v>
+        <v>1.576951217430178e-05</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2675153911113739</v>
+        <v>1.66649479069747e-05</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1306336522102356</v>
+        <v>4.929617261950625e-06</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02346836775541306</v>
+        <v>6.529173333547078e-06</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.1284819692373276</v>
+        <v>1.110102402890334e-05</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.05722158402204514</v>
+        <v>6.223217496881261e-06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.09100206196308136</v>
+        <v>1.217203316628002e-05</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.3262822926044464</v>
+        <v>5.333879926183727e-06</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.07301381230354309</v>
+        <v>1.167920800071442e-06</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1626662760972977</v>
+        <v>2.584639514680021e-05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1520562171936035</v>
+        <v>2.551522993599065e-05</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.04425539448857307</v>
+        <v>9.238349321094574e-07</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.09761732071638107</v>
+        <v>2.263240276079159e-06</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.3074899613857269</v>
+        <v>1.656166750763077e-05</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.01654454879462719</v>
+        <v>5.612229756479792e-07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.2580253481864929</v>
+        <v>1.16602150228573e-05</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.07614011317491531</v>
+        <v>2.527324249967933e-05</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.001968229189515114</v>
+        <v>2.974644985442865e-06</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.01295616291463375</v>
+        <v>8.76085050549591e-06</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.009712491184473038</v>
+        <v>7.052138244034722e-06</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.04028089717030525</v>
+        <v>5.979253273835639e-06</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.1047758758068085</v>
+        <v>3.584014393709367e-06</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.2267096638679504</v>
+        <v>4.55322333436925e-06</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.09208662807941437</v>
+        <v>1.665868239797419e-06</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.2140049636363983</v>
+        <v>2.640543607412837e-05</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.005555987358093</v>
+        <v>5.148704440216534e-05</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.1989931017160416</v>
+        <v>8.336495739058591e-06</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.3539938926696777</v>
+        <v>7.693026418564841e-06</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.3910732269287109</v>
+        <v>6.171555924083805e-06</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.06311778724193573</v>
+        <v>3.067434136028169e-06</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.2551296055316925</v>
+        <v>6.390848284354433e-06</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.08273018151521683</v>
+        <v>1.254201833944535e-05</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.09898612648248672</v>
+        <v>6.832929102529306e-06</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.2711561918258667</v>
+        <v>1.718530074867886e-05</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.08073873817920685</v>
+        <v>1.767429603205528e-05</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.2997004985809326</v>
+        <v>1.038995492308459e-06</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.2830593287944794</v>
+        <v>1.225263804371934e-05</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.3465195000171661</v>
+        <v>4.06760118494276e-05</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.2462309747934341</v>
+        <v>6.882026809762465e-06</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.2204594016075134</v>
+        <v>1.408164280292112e-05</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.6345166563987732</v>
+        <v>2.231873395430739e-06</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.1540269404649734</v>
+        <v>2.031702933891211e-06</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.03484664857387543</v>
+        <v>1.912738071041531e-06</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6154871582984924</v>
+        <v>6.573715836566407e-06</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.001740485429763794</v>
+        <v>1.835770831348782e-06</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.6533644795417786</v>
+        <v>8.710796464583836e-06</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.7857354879379272</v>
+        <v>1.118312957260059e-05</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.1905483454465866</v>
+        <v>1.284565496462164e-05</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.01684025675058365</v>
+        <v>1.590327883604914e-05</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.291817843914032</v>
+        <v>5.478453203977551e-06</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.06917299330234528</v>
+        <v>3.067982561333338e-07</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.07760173827409744</v>
+        <v>3.349224425619468e-05</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.4456788003444672</v>
+        <v>4.40925796283409e-05</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.158964067697525</v>
+        <v>5.87664044360281e-06</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.08793199062347412</v>
+        <v>1.454221001040423e-05</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.2582885026931763</v>
+        <v>9.055711416294798e-06</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.04736028611660004</v>
+        <v>8.715844160178676e-06</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.3982261121273041</v>
+        <v>3.82322832592763e-06</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.07723071426153183</v>
+        <v>1.623932621441782e-05</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.1321753859519958</v>
+        <v>4.43313774667331e-06</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.03539539873600006</v>
+        <v>1.729183168208692e-06</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.1816160976886749</v>
+        <v>6.541753919009352e-06</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.06303701549768448</v>
+        <v>1.583087851031451e-06</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.05066424608230591</v>
+        <v>3.549920165824005e-06</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.02212437987327576</v>
+        <v>4.127371539652813e-06</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.1411550641059875</v>
+        <v>8.339055966644082e-06</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.004385217092931271</v>
+        <v>5.131068405717087e-07</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.2317972183227539</v>
+        <v>3.051268322451506e-06</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.04404326900839806</v>
+        <v>3.123639316982008e-06</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.517646312713623</v>
+        <v>2.404721635684837e-05</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.5482860207557678</v>
+        <v>3.015144829987548e-05</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.02368859946727753</v>
+        <v>5.948779289610684e-06</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.2228859812021255</v>
+        <v>6.815498636569828e-06</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.6179128885269165</v>
+        <v>4.11393993999809e-05</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0298263393342495</v>
+        <v>1.012532356980955e-05</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0614863783121109</v>
+        <v>1.901215000543743e-05</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.2279060184955597</v>
+        <v>1.716744918667246e-05</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.04825352877378464</v>
+        <v>7.83897667133715e-06</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.01312214136123657</v>
+        <v>1.123443553296966e-06</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.1241174265742302</v>
+        <v>4.809343408851419e-06</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.08675140142440796</v>
+        <v>1.284641712118173e-06</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.1598922908306122</v>
+        <v>3.772150193981361e-06</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.03610655292868614</v>
+        <v>3.241118974983692e-06</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.1150492206215858</v>
+        <v>7.081348940118914e-06</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.02209520898759365</v>
+        <v>2.378015324211447e-06</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.1289655715227127</v>
+        <v>5.039330062572844e-06</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.000171992345713079</v>
+        <v>1.859251028690778e-06</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.5118924379348755</v>
+        <v>1.45845660881605e-06</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.707359790802002</v>
+        <v>5.206092282605823e-06</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.04452148824930191</v>
+        <v>4.214625732856803e-06</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.4016660451889038</v>
+        <v>1.747010173858143e-05</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1456683576107025</v>
+        <v>1.041640643961728e-05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.008732506074011326</v>
+        <v>5.747349860030226e-06</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.2871755659580231</v>
+        <v>7.21816604709602e-06</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.005766372662037611</v>
+        <v>4.736392384074861e-06</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.08710582554340363</v>
+        <v>2.602039603516459e-05</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.2867556214332581</v>
+        <v>1.316548514296301e-05</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.1767483353614807</v>
+        <v>5.582234734902158e-06</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.1557842940092087</v>
+        <v>1.848075044108555e-06</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.09559828788042068</v>
+        <v>7.142030881368555e-06</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.1108639016747475</v>
+        <v>4.416597676026868e-06</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.05500271543860435</v>
+        <v>1.39980156745878e-05</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.1441187709569931</v>
+        <v>2.406812882327358e-06</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.08936668932437897</v>
+        <v>5.374680767999962e-06</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.1204384416341782</v>
+        <v>3.893710527336225e-06</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.1463519930839539</v>
+        <v>4.98481767863268e-07</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.03315784782171249</v>
+        <v>2.229431174782803e-06</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.001645969226956367</v>
+        <v>1.156862708739936e-06</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.326093852519989</v>
+        <v>1.743735879244923e-06</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.06079817563295364</v>
+        <v>1.394880746374838e-05</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.1271513998508453</v>
+        <v>9.233112905349117e-07</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.1246958151459694</v>
+        <v>5.602276360150427e-06</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.2090392559766769</v>
+        <v>1.046719989972189e-05</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.1011323258280754</v>
+        <v>3.754837962333113e-06</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.0966283455491066</v>
+        <v>4.473536591831362e-06</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.05005073547363281</v>
+        <v>6.194152774696704e-06</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.00667902734130621</v>
+        <v>4.380331574793672e-06</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.3166289329528809</v>
+        <v>1.015631823975127e-05</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.1007967740297318</v>
+        <v>3.953809482482029e-06</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0813581794500351</v>
+        <v>5.476083970279433e-06</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.05641675740480423</v>
+        <v>7.150795681809541e-06</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.2287040799856186</v>
+        <v>1.582583081471967e-06</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.03997071459889412</v>
+        <v>5.601091856988205e-07</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.2095561176538467</v>
+        <v>3.39308598995558e-07</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.04250308126211166</v>
+        <v>8.811361112748273e-06</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.1456290781497955</v>
+        <v>7.383514457615092e-06</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0045052170753479</v>
+        <v>1.491490365879145e-06</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.1998366117477417</v>
+        <v>4.341926342021907e-06</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0627235621213913</v>
+        <v>1.1721053851943e-06</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.1090070456266403</v>
+        <v>9.317369404016063e-06</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.07589300721883774</v>
+        <v>7.597338480991311e-06</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.04513723403215408</v>
+        <v>6.960257451282814e-06</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.01683671958744526</v>
+        <v>1.084245013771579e-07</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1126291304826736</v>
+        <v>6.99094744049944e-06</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.04863322153687477</v>
+        <v>2.236497493868228e-06</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0876166895031929</v>
+        <v>4.191723746771459e-06</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.06892810761928558</v>
+        <v>2.502368261048105e-06</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.1382238864898682</v>
+        <v>7.009231921983883e-06</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.04998105019330978</v>
+        <v>8.085171430138871e-07</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.2290327548980713</v>
+        <v>6.120873877080157e-06</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.02537527307868004</v>
+        <v>5.591243279923219e-06</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.1809228360652924</v>
+        <v>8.407399036514107e-06</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.07211592048406601</v>
+        <v>2.663228997334954e-06</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.09214158356189728</v>
+        <v>7.49148239265196e-06</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.1153960451483727</v>
+        <v>1.210004575113999e-05</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.1794659495353699</v>
+        <v>7.091516181390034e-06</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.02097692340612411</v>
+        <v>1.038559730659472e-06</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.07424232363700867</v>
+        <v>2.316563040949404e-06</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.06795231252908707</v>
+        <v>5.974463874736102e-06</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.04796817898750305</v>
+        <v>1.321629952144576e-05</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.1764541864395142</v>
+        <v>1.274022906727623e-05</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.2838466763496399</v>
+        <v>3.24395987263415e-05</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.2318597435951233</v>
+        <v>2.340541868761647e-05</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.4895462393760681</v>
+        <v>1.692525415819546e-06</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.3676154315471649</v>
+        <v>2.688197855604813e-05</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.133421465754509</v>
+        <v>1.134389094659127e-05</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.2633978128433228</v>
+        <v>2.810338855852024e-06</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.1427219212055206</v>
+        <v>1.176865316665499e-05</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.08575734496116638</v>
+        <v>1.371199050481664e-05</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.1670346558094025</v>
+        <v>8.706307198735885e-06</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.3595616817474365</v>
+        <v>7.716605978203006e-06</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.03768039494752884</v>
+        <v>6.889692031109007e-06</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.3008478581905365</v>
+        <v>2.310855415998958e-05</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.2074195593595505</v>
+        <v>1.732623604766559e-05</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.08197572082281113</v>
+        <v>1.718304247333435e-06</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.1032343581318855</v>
+        <v>2.160189296773751e-06</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.3269290328025818</v>
+        <v>7.497429123759503e-06</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.1022303476929665</v>
+        <v>1.831957661124761e-06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.1785058975219727</v>
+        <v>0.4699302315711975</v>
       </c>
       <c r="B11" t="n">
-        <v>0.36905437707901</v>
+        <v>0.4705702662467957</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03300226107239723</v>
+        <v>0.2215832471847534</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02122209221124649</v>
+        <v>0.07921303808689117</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0581580214202404</v>
+        <v>0.1442129164934158</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1258778870105743</v>
+        <v>0.08828486502170563</v>
       </c>
       <c r="G11" t="n">
-        <v>0.05531566590070724</v>
+        <v>0.1046260595321655</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09837895631790161</v>
+        <v>0.01127652451395988</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07466897368431091</v>
+        <v>0.149794340133667</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1324661672115326</v>
+        <v>0.2597217261791229</v>
       </c>
       <c r="K11" t="n">
-        <v>0.278268963098526</v>
+        <v>0.7569112777709961</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04064899682998657</v>
+        <v>0.073785200715065</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0919039249420166</v>
+        <v>0.2321372032165527</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2809614241123199</v>
+        <v>0.2213154137134552</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2070109248161316</v>
+        <v>0.01755794696509838</v>
       </c>
       <c r="P11" t="n">
-        <v>0.12481589615345</v>
+        <v>0.01343342661857605</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2865845561027527</v>
+        <v>0.3058740794658661</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1100522577762604</v>
+        <v>0.2259299010038376</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02830346487462521</v>
+        <v>0.03762618452310562</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1984046846628189</v>
+        <v>0.1681170761585236</v>
       </c>
       <c r="U11" t="n">
-        <v>0.04665237292647362</v>
+        <v>0.179972842335701</v>
       </c>
       <c r="V11" t="n">
-        <v>0.04504648596048355</v>
+        <v>0.1108619272708893</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1554616391658783</v>
+        <v>0.1162215694785118</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1055161133408546</v>
+        <v>0.1343777030706406</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.04069948941469193</v>
+        <v>0.02901440300047398</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.007867119275033474</v>
+        <v>0.0649254322052002</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.03440010920166969</v>
+        <v>0.004759699106216431</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.003878947347402573</v>
+        <v>0.2054895609617233</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0913935974240303</v>
+        <v>0.2318299412727356</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.05784723535180092</v>
+        <v>0.2220323979854584</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.1506589204072952</v>
+        <v>0.1567049622535706</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.08664491772651672</v>
+        <v>0.1824536025524139</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.1498627513647079</v>
+        <v>0.1411896497011185</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.1266684532165527</v>
+        <v>0.04850655049085617</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.06227865442633629</v>
+        <v>0.2531194984912872</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.01503893919289112</v>
+        <v>0.01156288012862206</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.1014063507318497</v>
+        <v>0.008995313197374344</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.1049103587865829</v>
+        <v>0.2924140691757202</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.02938035875558853</v>
+        <v>0.09731504321098328</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.03483988344669342</v>
+        <v>0.03112209215760231</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.05470554903149605</v>
+        <v>0.0202007070183754</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.09756646305322647</v>
+        <v>0.1118782609701157</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.1156919598579407</v>
+        <v>0.03877848014235497</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.09879714995622635</v>
+        <v>0.2109847962856293</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.05509399622678757</v>
+        <v>0.004892915952950716</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.1766034662723541</v>
+        <v>0.06556053459644318</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.4033888280391693</v>
+        <v>0.6313824653625488</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.05088284984230995</v>
+        <v>0.113151840865612</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.03980614244937897</v>
+        <v>0.0970216691493988</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.2543260753154755</v>
+        <v>0.04278208315372467</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.0007480606436729431</v>
+        <v>0.02718041837215424</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.00413201842457056</v>
+        <v>0.002098641358315945</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.09203361719846725</v>
+        <v>0.01907350122928619</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.07550526410341263</v>
+        <v>0.05647700279951096</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.1262698024511337</v>
+        <v>0.5198656916618347</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.01670357584953308</v>
+        <v>0.1775268614292145</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.04335686191916466</v>
+        <v>0.2459902465343475</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.06795505434274673</v>
+        <v>0.03344712033867836</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.2363910228013992</v>
+        <v>0.3833087682723999</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.08203434944152832</v>
+        <v>0.04378724470734596</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.07061326503753662</v>
+        <v>0.004267133772373199</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.2195236384868622</v>
+        <v>0.1237076371908188</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.1079051569104195</v>
+        <v>0.129509225487709</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.04298045858740807</v>
+        <v>0.07993442565202713</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1441498994827271</v>
+        <v>0.2913461327552795</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.01703748293220997</v>
+        <v>0.05635380744934082</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.2245606482028961</v>
+        <v>0.05816527456045151</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.3627542555332184</v>
+        <v>0.1581136137247086</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.1031613945960999</v>
+        <v>0.2658593356609344</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.02812028676271439</v>
+        <v>0.1944561749696732</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.1772933751344681</v>
+        <v>0.001049723476171494</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.1160843297839165</v>
+        <v>0.0248627383261919</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.085245281457901</v>
+        <v>0.1485646963119507</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.2182473987340927</v>
+        <v>0.6467984318733215</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.008310504257678986</v>
+        <v>0.2260768860578537</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.06547863781452179</v>
+        <v>0.1326098442077637</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.06882446259260178</v>
+        <v>0.005381234921514988</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.03274517878890038</v>
+        <v>0.01693618297576904</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.134245753288269</v>
+        <v>0.1508497595787048</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.04800796136260033</v>
+        <v>0.05379100888967514</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.02041643299162388</v>
+        <v>0.05604191869497299</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0143684558570385</v>
+        <v>0.08223249018192291</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.07027826458215714</v>
+        <v>0.2081512659788132</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.02102119289338589</v>
+        <v>0.1075678914785385</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.05571596324443817</v>
+        <v>0.03313247114419937</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01974327303469181</v>
+        <v>0.01796471700072289</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.005046356935054064</v>
+        <v>0.06252474337816238</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.003301255404949188</v>
+        <v>0.004295525141060352</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.003713787999004126</v>
+        <v>0.008945598267018795</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.01279300823807716</v>
+        <v>0.02472760155797005</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.1911555826663971</v>
+        <v>0.1127564087510109</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.1391775161027908</v>
+        <v>0.4785165786743164</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.02104791253805161</v>
+        <v>0.004149638116359711</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.04821667447686195</v>
+        <v>0.1411072611808777</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.2453827857971191</v>
+        <v>0.1845415830612183</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.01993242651224136</v>
+        <v>0.1773972660303116</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.08484429121017456</v>
+        <v>0.05141705274581909</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.01550243515521288</v>
+        <v>0.1242293193936348</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.05228736996650696</v>
+        <v>0.000952886592131108</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.004819903522729874</v>
+        <v>0.03708374127745628</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.0749894455075264</v>
+        <v>0.1973735392093658</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.01664065755903721</v>
+        <v>0.1109028235077858</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.07524070143699646</v>
+        <v>0.04496270418167114</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0004792466061189771</v>
+        <v>0.02889436669647694</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.03525016084313393</v>
+        <v>0.02104425057768822</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.02778257802128792</v>
+        <v>0.01091901306062937</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.02747885882854462</v>
+        <v>0.003797533921897411</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.01158794201910496</v>
+        <v>0.01650289818644524</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.2552921772003174</v>
+        <v>0.03548348695039749</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.4576517343521118</v>
+        <v>0.6073166131973267</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.01689344085752964</v>
+        <v>0.0881141722202301</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.06083082407712936</v>
+        <v>0.1917136162519455</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01556211896240711</v>
+        <v>0.04465937614440918</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.2255039066076279</v>
+        <v>0.09668977558612823</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.1635230630636215</v>
+        <v>0.007269042078405619</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.06466761231422424</v>
+        <v>0.09420005977153778</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.1243377551436424</v>
+        <v>0.01521116122603416</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.1008214950561523</v>
+        <v>0.02159490436315536</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.1428093016147614</v>
+        <v>0.07927058637142181</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.02507951855659485</v>
+        <v>0.008551942184567451</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.1083962544798851</v>
+        <v>0.01976856589317322</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.08816306293010712</v>
+        <v>0.1263243108987808</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.005506303161382675</v>
+        <v>0.07578250020742416</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.09495318681001663</v>
+        <v>0.01896855235099792</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.005987959448248148</v>
+        <v>0.06182228401303291</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.07919382303953171</v>
+        <v>0.004118410870432854</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.04015098884701729</v>
+        <v>0.2532888650894165</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.06342427432537079</v>
+        <v>0.3085605502128601</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.07610840350389481</v>
+        <v>0.1519962400197983</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.1430927217006683</v>
+        <v>0.04621315747499466</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.06801983714103699</v>
+        <v>0.1204156279563904</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.05497930943965912</v>
+        <v>0.06658671051263809</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.08960016071796417</v>
+        <v>0.04320887848734856</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.05631193146109581</v>
+        <v>0.09353207796812057</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.06849435716867447</v>
+        <v>0.139166072010994</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.06361579149961472</v>
+        <v>0.07774756103754044</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.1302297562360764</v>
+        <v>0.006927825510501862</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.01752036437392235</v>
+        <v>0.03860289603471756</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.07230142503976822</v>
+        <v>0.02253953740000725</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01435679756104946</v>
+        <v>0.07932547479867935</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.07033649832010269</v>
+        <v>0.06380840390920639</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.05618277937173843</v>
+        <v>0.001383045688271523</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.03618621081113815</v>
+        <v>0.06513939052820206</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.02653607726097107</v>
+        <v>0.005515212658792734</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.05040245875716209</v>
+        <v>0.009941399097442627</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.001931716222316027</v>
+        <v>0.1282493472099304</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.007393855601549149</v>
+        <v>0.01503267139196396</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.002949799410998821</v>
+        <v>0.08352091908454895</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.01516387425363064</v>
+        <v>0.1792090386152267</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.04564440250396729</v>
+        <v>0.09166170656681061</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.03662963956594467</v>
+        <v>0.06360305100679398</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.04398331418633461</v>
+        <v>0.01214740052819252</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.06001998856663704</v>
+        <v>0.03973454982042313</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.02210699766874313</v>
+        <v>0.05895199999213219</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.05808040499687195</v>
+        <v>0.2538587152957916</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.009572026319801807</v>
+        <v>0.104488767683506</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.05506433174014091</v>
+        <v>0.001836022362112999</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.03024112805724144</v>
+        <v>0.04440408572554588</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.02261793427169323</v>
+        <v>0.0348065122961998</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.007103001698851585</v>
+        <v>0.01346954796463251</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.02340796589851379</v>
+        <v>0.0135503550991416</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.001576860435307026</v>
+        <v>0.03547466546297073</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.1372915506362915</v>
+        <v>0.07870049774646759</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.07758759707212448</v>
+        <v>0.039471335709095</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0358884334564209</v>
+        <v>0.02738414518535137</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.1101730987429619</v>
+        <v>0.1628992855548859</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.02894258499145508</v>
+        <v>0.0449180081486702</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.0004274533130228519</v>
+        <v>0.1546581089496613</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.01653508096933365</v>
+        <v>0.07570275664329529</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.03398001939058304</v>
+        <v>0.06666450947523117</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.05197087302803993</v>
+        <v>0.03245612233877182</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.04627938568592072</v>
+        <v>0.05626151710748672</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.04835402593016624</v>
+        <v>0.1201383471488953</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.05593550205230713</v>
+        <v>0.01692162826657295</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.1917947828769684</v>
+        <v>0.1416949033737183</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.178268238902092</v>
+        <v>0.6272382736206055</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.03263234719634056</v>
+        <v>0.07953722774982452</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.009676225483417511</v>
+        <v>0.01043839380145073</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.02924420684576035</v>
+        <v>0.008579488843679428</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0722920298576355</v>
+        <v>0.1065381914377213</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.02783397398889065</v>
+        <v>0.07594605535268784</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.1579596549272537</v>
+        <v>0.2015620172023773</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.04145868867635727</v>
+        <v>0.02812022157013416</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.2370077967643738</v>
+        <v>0.008201991207897663</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.2696269452571869</v>
+        <v>0.2387422621250153</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.08622848242521286</v>
+        <v>0.03876703977584839</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.1797463297843933</v>
+        <v>0.1239009499549866</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.2500349283218384</v>
+        <v>0.0743815153837204</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.03324348479509354</v>
+        <v>0.06637264043092728</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.001688490272499621</v>
+        <v>0.4438592791557312</v>
       </c>
       <c r="B12" t="n">
-        <v>0.159101814031601</v>
+        <v>0.02237697690725327</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01414323877543211</v>
+        <v>0.212152436375618</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03712310642004013</v>
+        <v>0.06162847578525543</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04584396257996559</v>
+        <v>0.410766214132309</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0351158119738102</v>
+        <v>5.19193708896637e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06603056192398071</v>
+        <v>0.4892672896385193</v>
       </c>
       <c r="H12" t="n">
-        <v>0.002354292897507548</v>
+        <v>0.5714364051818848</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01572060212492943</v>
+        <v>0.3012327253818512</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02223145216703415</v>
+        <v>0.3797032237052917</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1157499179244041</v>
+        <v>0.2421562373638153</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005694691557437181</v>
+        <v>0.5686721205711365</v>
       </c>
       <c r="M12" t="n">
-        <v>0.07475157827138901</v>
+        <v>0.138517439365387</v>
       </c>
       <c r="N12" t="n">
-        <v>0.05142901092767715</v>
+        <v>0.3495526313781738</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04437564313411713</v>
+        <v>0.3072059154510498</v>
       </c>
       <c r="P12" t="n">
-        <v>0.05905909091234207</v>
+        <v>0.6688082218170166</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.01864754967391491</v>
+        <v>0.6458885669708252</v>
       </c>
       <c r="R12" t="n">
-        <v>0.003173728240653872</v>
+        <v>0.03607749938964844</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01976953819394112</v>
+        <v>0.145879715681076</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04402253031730652</v>
+        <v>0.112124040722847</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0007345877820625901</v>
+        <v>0.1383295059204102</v>
       </c>
       <c r="V12" t="n">
-        <v>0.004908669274300337</v>
+        <v>0.0002226363867521286</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03945431113243103</v>
+        <v>0.1004357039928436</v>
       </c>
       <c r="X12" t="n">
-        <v>0.02913609147071838</v>
+        <v>0.01655945181846619</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.003780201077461243</v>
+        <v>0.136664941906929</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.008325269445776939</v>
+        <v>0.05711401253938675</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.01360843703150749</v>
+        <v>0.1943816095590591</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.01737248338758945</v>
+        <v>0.2735262513160706</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.03802994266152382</v>
+        <v>0.3317143619060516</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.005451198201626539</v>
+        <v>0.3094022870063782</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.002349270507693291</v>
+        <v>0.01676378771662712</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.008256056345999241</v>
+        <v>0.482007771730423</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.009722014889121056</v>
+        <v>0.304209977388382</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0003464808687567711</v>
+        <v>0.1065008938312531</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.003527581226080656</v>
+        <v>0.00745135173201561</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.01261954102665186</v>
+        <v>0.05176983773708344</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.01860169135034084</v>
+        <v>0.1991353034973145</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.01918607391417027</v>
+        <v>0.344184935092926</v>
       </c>
       <c r="AM12" t="n">
-        <v>5.441508983494714e-05</v>
+        <v>0.1572550088167191</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.01820056140422821</v>
+        <v>0.0186002105474472</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.007887687534093857</v>
+        <v>0.0599508062005043</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.007862799800932407</v>
+        <v>0.09440643340349197</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.00902960542589426</v>
+        <v>0.1023576259613037</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.003606651909649372</v>
+        <v>0.001576557755470276</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.005070412997156382</v>
+        <v>0.1456788629293442</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.04168966040015221</v>
+        <v>0.4022335410118103</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1328303068876266</v>
+        <v>0.72002774477005</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.001207308028824627</v>
+        <v>0.2810295820236206</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.03701679781079292</v>
+        <v>0.2543680667877197</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.002654870972037315</v>
+        <v>0.1511295288801193</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.02395100705325603</v>
+        <v>0.3574485182762146</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.01936038210988045</v>
+        <v>0.03990759700536728</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.01627752371132374</v>
+        <v>0.2475616782903671</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.009917463175952435</v>
+        <v>0.02901706472039223</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.01207627728581429</v>
+        <v>0.1012390851974487</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03436477854847908</v>
+        <v>0.5993339419364929</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.04461120069026947</v>
+        <v>0.2328783124685287</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.03176257386803627</v>
+        <v>0.01992778480052948</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.03791063278913498</v>
+        <v>0.58852618932724</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.01957163959741592</v>
+        <v>0.07553267478942871</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.02464037016034126</v>
+        <v>0.1872929036617279</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.02550322189927101</v>
+        <v>0.3552036285400391</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.006380021572113037</v>
+        <v>0.2375855594873428</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.006125720217823982</v>
+        <v>0.1025744751095772</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.04105276614427567</v>
+        <v>0.03769095987081528</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.02683715522289276</v>
+        <v>0.08167111873626709</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.01799601688981056</v>
+        <v>0.2111417800188065</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.05863278731703758</v>
+        <v>0.21967813372612</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0142814964056015</v>
+        <v>0.3256836235523224</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.01209710538387299</v>
+        <v>0.221946656703949</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.01392101123929024</v>
+        <v>0.009338416159152985</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.006474705412983894</v>
+        <v>0.1453200578689575</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.01668269373476505</v>
+        <v>0.3255124092102051</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.06114602088928223</v>
+        <v>0.4906980395317078</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.02510211616754532</v>
+        <v>0.233598455786705</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.01798036135733128</v>
+        <v>0.09070428460836411</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0003354632353875786</v>
+        <v>0.05892522633075714</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.01682025007903576</v>
+        <v>0.03240018710494041</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.004320337437093258</v>
+        <v>0.01041945815086365</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.02399128675460815</v>
+        <v>0.1685715019702911</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.01136272773146629</v>
+        <v>0.04379117861390114</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.004400121048092842</v>
+        <v>0.08259538561105728</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.03303417563438416</v>
+        <v>0.008802905678749084</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.0141065726056695</v>
+        <v>0.06116664037108421</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.01812286302447319</v>
+        <v>0.07357917726039886</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.001793672563508153</v>
+        <v>0.1028222665190697</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.007304257247596979</v>
+        <v>0.06144211068749428</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.01182798948138952</v>
+        <v>0.0567876324057579</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.001714748097583652</v>
+        <v>0.05444695055484772</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.01099538803100586</v>
+        <v>0.1458796411752701</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.03837748989462852</v>
+        <v>0.07081687450408936</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.04898605495691299</v>
+        <v>0.2039102464914322</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.003926637582480907</v>
+        <v>0.3907265663146973</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.003334484063088894</v>
+        <v>0.12005315721035</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.03675209358334541</v>
+        <v>0.2266406863927841</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.01858034916222095</v>
+        <v>0.01691567897796631</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.005264658946543932</v>
+        <v>0.3411114811897278</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.003736663609743118</v>
+        <v>0.1974087208509445</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.01184309646487236</v>
+        <v>0.1401640772819519</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.007126828655600548</v>
+        <v>0.0587007999420166</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0264835674315691</v>
+        <v>0.02287460118532181</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.01909744925796986</v>
+        <v>0.04831068217754364</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.02615599893033504</v>
+        <v>0.05004008114337921</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.0004525885451585054</v>
+        <v>0.1057347506284714</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.002893470693379641</v>
+        <v>0.05146071314811707</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.01571739464998245</v>
+        <v>0.0844549834728241</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.002777354326099157</v>
+        <v>0.07729436457157135</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.009013029746711254</v>
+        <v>0.102049820125103</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.007290550507605076</v>
+        <v>0.1187919527292252</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.08557961136102676</v>
+        <v>0.1035880595445633</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.01562272105365992</v>
+        <v>0.3173674941062927</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.03599465265870094</v>
+        <v>0.1658597886562347</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.03495074063539505</v>
+        <v>0.01555525325238705</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.009997123852372169</v>
+        <v>0.1324344277381897</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.02597737312316895</v>
+        <v>0.1548521667718887</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.01238163281232119</v>
+        <v>0.2936508059501648</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.02586708962917328</v>
+        <v>0.03365817293524742</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.001789045054465532</v>
+        <v>0.1086301207542419</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.02159805782139301</v>
+        <v>0.04514045268297195</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.01956662721931934</v>
+        <v>0.1200178787112236</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.004619236569851637</v>
+        <v>0.3057330250740051</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.01042799837887287</v>
+        <v>0.2365500330924988</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.005256003700196743</v>
+        <v>0.3963905274868011</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.01039673294872046</v>
+        <v>0.1613402962684631</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.001100389519706368</v>
+        <v>0.008650136180222034</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.009880665689706802</v>
+        <v>0.13267482817173</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.003769258502870798</v>
+        <v>0.01721153408288956</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.02077572420239449</v>
+        <v>0.03759399801492691</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.01020885724574327</v>
+        <v>0.001912252977490425</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.01907014846801758</v>
+        <v>0.06866922974586487</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.01738466881215572</v>
+        <v>0.1790347695350647</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.002568985335528851</v>
+        <v>0.1354691237211227</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.003600560361519456</v>
+        <v>0.01368474867194891</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.01984313316643238</v>
+        <v>0.1952303349971771</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.006250106729567051</v>
+        <v>0.1334778368473053</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0143508818000555</v>
+        <v>0.06689085066318512</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.006254241801798344</v>
+        <v>0.04388967901468277</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.009737790562212467</v>
+        <v>0.009810625575482845</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.02631752379238605</v>
+        <v>0.09054917097091675</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.002300365129485726</v>
+        <v>0.01686307415366173</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.008708580397069454</v>
+        <v>0.007149579003453255</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.01571605540812016</v>
+        <v>0.05706349760293961</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.01237637829035521</v>
+        <v>0.02940134331583977</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.003925780300050974</v>
+        <v>0.09484170377254486</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.01950212195515633</v>
+        <v>0.2228305041790009</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.01152659673243761</v>
+        <v>0.0138540230691433</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.02685341611504555</v>
+        <v>0.06332562863826752</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.02031692489981651</v>
+        <v>0.2753061652183533</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.009315925650298595</v>
+        <v>0.0004391390830278397</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.009850376285612583</v>
+        <v>0.0697576105594635</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.01505731232464314</v>
+        <v>0.1235444396734238</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.008203685283660889</v>
+        <v>0.05648132041096687</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.0002028846647590399</v>
+        <v>0.08357890695333481</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.006819674279540777</v>
+        <v>0.05462662130594254</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.02569280937314034</v>
+        <v>0.002274302765727043</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.01383678521960974</v>
+        <v>0.02205239608883858</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0191070307046175</v>
+        <v>0.003122743917629123</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.00273720221593976</v>
+        <v>0.0693708211183548</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.007142956368625164</v>
+        <v>0.002163257915526628</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.01826029643416405</v>
+        <v>0.04375246912240982</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.004827022552490234</v>
+        <v>0.111820288002491</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.01190976239740849</v>
+        <v>0.1056831553578377</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.01924579776823521</v>
+        <v>0.2598938941955566</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.0077784089371562</v>
+        <v>0.1022077649831772</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.01439963467419147</v>
+        <v>0.1495195329189301</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.01130003295838833</v>
+        <v>0.2296127378940582</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.01829403452575207</v>
+        <v>0.1392754018306732</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.0145176388323307</v>
+        <v>0.1496013551950455</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.001429123105481267</v>
+        <v>0.07733573764562607</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.01083183754235506</v>
+        <v>0.170091986656189</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.00633748946711421</v>
+        <v>0.5074097514152527</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.01036070287227631</v>
+        <v>0.05859707295894623</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.02048853412270546</v>
+        <v>0.4371852576732635</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.009839354082942009</v>
+        <v>0.5758076310157776</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.02955874800682068</v>
+        <v>0.3263233006000519</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.02938451245427132</v>
+        <v>0.1902791261672974</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.01499487925320864</v>
+        <v>0.4128232598304749</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.03535845130681992</v>
+        <v>0.2643940448760986</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.03175776079297066</v>
+        <v>0.251709371805191</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.008741865865886211</v>
+        <v>0.2222136408090591</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.02666060253977776</v>
+        <v>0.09369977563619614</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.01877139136195183</v>
+        <v>0.1867480278015137</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.004370822571218014</v>
+        <v>0.1551727950572968</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.02195832505822182</v>
+        <v>0.1354472637176514</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.00921123381704092</v>
+        <v>0.293448805809021</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.01033216156065464</v>
+        <v>0.0380493625998497</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.03217199444770813</v>
+        <v>0.1403641700744629</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.02657701261341572</v>
+        <v>0.09943301230669022</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.01764890365302563</v>
+        <v>0.07356052845716476</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.007300319150090218</v>
+        <v>0.08476519584655762</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1024684906005859</v>
+        <v>0.2828022241592407</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01497443020343781</v>
+        <v>0.02393120899796486</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03515619039535522</v>
+        <v>0.05990725755691528</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02004498615860939</v>
+        <v>0.3154008388519287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.009340878576040268</v>
+        <v>0.2459452450275421</v>
       </c>
       <c r="G13" t="n">
-        <v>0.006242242176085711</v>
+        <v>0.1401817351579666</v>
       </c>
       <c r="H13" t="n">
-        <v>0.003962090238928795</v>
+        <v>0.1742654740810394</v>
       </c>
       <c r="I13" t="n">
-        <v>0.03367041423916817</v>
+        <v>0.10529875010252</v>
       </c>
       <c r="J13" t="n">
-        <v>0.009304896928369999</v>
+        <v>0.02733641676604748</v>
       </c>
       <c r="K13" t="n">
-        <v>0.07652039080858231</v>
+        <v>0.4148411750793457</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00182335777208209</v>
+        <v>0.03239119797945023</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03872751817107201</v>
+        <v>0.09087274223566055</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03684426471590996</v>
+        <v>0.361514687538147</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01640619151294231</v>
+        <v>0.2917270064353943</v>
       </c>
       <c r="P13" t="n">
-        <v>0.009514125995337963</v>
+        <v>0.1603812128305435</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01293019019067287</v>
+        <v>0.05605867877602577</v>
       </c>
       <c r="R13" t="n">
-        <v>0.02644253894686699</v>
+        <v>0.111136756837368</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001205906271934509</v>
+        <v>0.02119708992540836</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02315506525337696</v>
+        <v>0.1052384376525879</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01560514885932207</v>
+        <v>0.002440465148538351</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01161738019436598</v>
+        <v>0.1890314370393753</v>
       </c>
       <c r="W13" t="n">
-        <v>0.001577997580170631</v>
+        <v>0.1364755183458328</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01574217900633812</v>
+        <v>0.05141887068748474</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.004064628388732672</v>
+        <v>0.003980971872806549</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.001917281886562705</v>
+        <v>0.0002762698568403721</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.005962957162410021</v>
+        <v>0.06898731738328934</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.009422088041901588</v>
+        <v>0.03025786578655243</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01811624504625797</v>
+        <v>0.09051059931516647</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.2093765437603e-05</v>
+        <v>0.09334740042686462</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.004130945540964603</v>
+        <v>0.08552657812833786</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.000468347454443574</v>
+        <v>0.1540583074092865</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.008268686942756176</v>
+        <v>0.0880684107542038</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.004891940392553806</v>
+        <v>0.03252160176634789</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.01083364710211754</v>
+        <v>0.2150104641914368</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.002147099236026406</v>
+        <v>0.01544474065303802</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.008504413068294525</v>
+        <v>0.01012555230408907</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.009106971323490143</v>
+        <v>0.2161944955587387</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.006021879147738218</v>
+        <v>0.01701414585113525</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0005405023694038391</v>
+        <v>0.08485547453165054</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0105886422097683</v>
+        <v>0.1526165455579758</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.01094288378953934</v>
+        <v>0.04586430266499519</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.006308941636234522</v>
+        <v>0.0295008085668087</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.002118770033121109</v>
+        <v>0.1150939613580704</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.002146846847608685</v>
+        <v>0.00784595962613821</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.008818202652037144</v>
+        <v>0.1031033769249916</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0774107426404953</v>
+        <v>0.7158827781677246</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.002114470116794109</v>
+        <v>0.007955778390169144</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.00346939149312675</v>
+        <v>0.003611672669649124</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.003437809646129608</v>
+        <v>0.01622089743614197</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0002769315615296364</v>
+        <v>0.1356781870126724</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.007605468854308128</v>
+        <v>0.04362377896904945</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.001920527429319918</v>
+        <v>0.04611992835998535</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.009330982342362404</v>
+        <v>0.002558589447289705</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.003116061678156257</v>
+        <v>0.159649670124054</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.02606865018606186</v>
+        <v>0.2556291222572327</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.01802277006208897</v>
+        <v>0.1226492375135422</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.00608340697363019</v>
+        <v>0.08998657763004303</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.03173185512423515</v>
+        <v>0.3017580509185791</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.01853996515274048</v>
+        <v>0.01060369238257408</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.002463091164827347</v>
+        <v>0.02459689229726791</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.01574885100126266</v>
+        <v>0.07134734094142914</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01107868552207947</v>
+        <v>0.01870392262935638</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.008935709483921528</v>
+        <v>0.03127484023571014</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.02323221229016781</v>
+        <v>0.09794869273900986</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.008933951146900654</v>
+        <v>0.020845802500844</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.0004706284962594509</v>
+        <v>0.09531247615814209</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.03861415013670921</v>
+        <v>0.135720506310463</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.02020284533500671</v>
+        <v>0.05859263613820076</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0002664842177182436</v>
+        <v>0.2828619182109833</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.006348145194351673</v>
+        <v>0.03545748814940453</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0008488569874316454</v>
+        <v>0.01458519510924816</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.004633675795048475</v>
+        <v>0.09114785492420197</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.04599640145897865</v>
+        <v>0.4272575378417969</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.01049824338406324</v>
+        <v>0.0003596586175262928</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.008103892207145691</v>
+        <v>0.2032911330461502</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.005540604703128338</v>
+        <v>0.1271664500236511</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0203399732708931</v>
+        <v>0.07801326364278793</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.01247287914156914</v>
+        <v>0.05331680551171303</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.001185955130495131</v>
+        <v>0.01430814899504185</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.01127776969224215</v>
+        <v>0.094309963285923</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0008749660337343812</v>
+        <v>0.006950865499675274</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0203244611620903</v>
+        <v>0.1543470919132233</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.001086320262402296</v>
+        <v>0.01889410614967346</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.007734540849924088</v>
+        <v>0.01257544197142124</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.002660314086824656</v>
+        <v>0.04499160498380661</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0008139926358126104</v>
+        <v>0.04155177250504494</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0005830836016684771</v>
+        <v>0.06596536934375763</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.003005616832524538</v>
+        <v>0.01033705193549395</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.009390599094331264</v>
+        <v>0.02376816049218178</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.02700105868279934</v>
+        <v>0.1522725224494934</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0331643782556057</v>
+        <v>0.4028687477111816</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.0009251152514480054</v>
+        <v>0.133114755153656</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.006586376111954451</v>
+        <v>0.2405131012201309</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01544724684208632</v>
+        <v>0.07810448110103607</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.007022744044661522</v>
+        <v>0.06087737902998924</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.006775726098567247</v>
+        <v>0.1327088624238968</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.02395170927047729</v>
+        <v>0.0002088728360831738</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.001390285789966583</v>
+        <v>0.001248255372047424</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0010843361960724</v>
+        <v>0.04401930049061775</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.01662189699709415</v>
+        <v>0.1289677917957306</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.005432597827166319</v>
+        <v>0.02050605043768883</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.009954577311873436</v>
+        <v>0.02457693964242935</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.001310159801505506</v>
+        <v>0.03643301129341125</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.003004374215379357</v>
+        <v>0.04184799641370773</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0008252315456047654</v>
+        <v>0.02824554219841957</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.001055572647601366</v>
+        <v>0.004095862619578838</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.007485161069780588</v>
+        <v>0.0233894232660532</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.01766287907958031</v>
+        <v>0.1685333997011185</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.06198115274310112</v>
+        <v>0.07795628905296326</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.01082515995949507</v>
+        <v>0.02254746109247208</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.03278730809688568</v>
+        <v>0.2003248333930969</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.001854595029726624</v>
+        <v>0.008511267602443695</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.002386806532740593</v>
+        <v>0.00810280442237854</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.02838025987148285</v>
+        <v>0.09698060899972916</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.007911005988717079</v>
+        <v>0.1760424077510834</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.009793498553335667</v>
+        <v>0.02121893130242825</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.01089006848633289</v>
+        <v>0.0003378428518772125</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.01690211519598961</v>
+        <v>0.04043804109096527</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.009393934160470963</v>
+        <v>0.09963800013065338</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0108198057860136</v>
+        <v>0.1337652951478958</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.004626923240721226</v>
+        <v>0.07792487740516663</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.00015774488565512</v>
+        <v>0.02006100304424763</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.01601033098995686</v>
+        <v>0.004115293733775616</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.000568960327655077</v>
+        <v>0.077089823782444</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0009788554161787033</v>
+        <v>0.03445248305797577</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.007530909962952137</v>
+        <v>0.01984533667564392</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.008208848536014557</v>
+        <v>0.1876387596130371</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.007599435746669769</v>
+        <v>0.121037483215332</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.01095868740230799</v>
+        <v>0.06117428094148636</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.01220301259309053</v>
+        <v>0.1210077181458473</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.006329883821308613</v>
+        <v>0.1054698079824448</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.007798361126333475</v>
+        <v>0.03771066293120384</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.006559804547578096</v>
+        <v>0.07331512123346329</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.001283975783735514</v>
+        <v>0.08079712837934494</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.003323472803458571</v>
+        <v>0.05376055836677551</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.00162770738825202</v>
+        <v>0.03635792061686516</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.002333988668397069</v>
+        <v>0.02822422236204147</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.00702236220240593</v>
+        <v>0.051790751516819</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.005496210884302855</v>
+        <v>0.01348385587334633</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.002422275952994823</v>
+        <v>0.08377131819725037</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.004390723071992397</v>
+        <v>0.024599963799119</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.001636582193896174</v>
+        <v>0.003525551408529282</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.009670191444456577</v>
+        <v>0.01606833748519421</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.009305817075073719</v>
+        <v>0.03110605664551258</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.008745322935283184</v>
+        <v>0.09896600246429443</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.008263245224952698</v>
+        <v>0.02249516360461712</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.01068570837378502</v>
+        <v>0.04193117842078209</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.007851151749491692</v>
+        <v>0.02341468632221222</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.01717545092105865</v>
+        <v>0.05275102332234383</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.005525195971131325</v>
+        <v>0.04470257088541985</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.01010089553892612</v>
+        <v>0.08896589279174805</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.006277552340179682</v>
+        <v>0.06244844198226929</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0001060210634022951</v>
+        <v>0.0189993791282177</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.01777738705277443</v>
+        <v>0.1699292063713074</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.002635627053678036</v>
+        <v>0.02613355219364166</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.008414763025939465</v>
+        <v>0.02819801494479179</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.00185228290501982</v>
+        <v>0.03795813024044037</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.005376082379370928</v>
+        <v>0.04722852632403374</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.002475484274327755</v>
+        <v>0.07055608183145523</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.003373289946466684</v>
+        <v>0.004705513827502728</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.006776021793484688</v>
+        <v>0.0338902659714222</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.005963819101452827</v>
+        <v>0.07639853656291962</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.006983952596783638</v>
+        <v>0.08875305205583572</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.001519196899607778</v>
+        <v>0.02854305692017078</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.008643047884106636</v>
+        <v>0.1539837867021561</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.007730145938694477</v>
+        <v>0.08505950123071671</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.003297658171504736</v>
+        <v>0.03460235521197319</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.006001310423016548</v>
+        <v>0.05782197415828705</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.006171479821205139</v>
+        <v>0.1383225619792938</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0137381674721837</v>
+        <v>0.01056556589901447</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.00522723188623786</v>
+        <v>0.06976016610860825</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.009938585571944714</v>
+        <v>0.1455097496509552</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.01311207190155983</v>
+        <v>0.002032995223999023</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.007269259542226791</v>
+        <v>0.1133239418268204</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01672408729791641</v>
+        <v>0.2761134803295135</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.01399124134331942</v>
+        <v>0.1044573932886124</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.001446743961423635</v>
+        <v>0.01734080165624619</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.006667444482445717</v>
+        <v>0.126240074634552</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.005554037634283304</v>
+        <v>0.04138795658946037</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.004347075242549181</v>
+        <v>0.007207700051367283</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0229545496404171</v>
+        <v>0.0141759030520916</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.01245952676981688</v>
+        <v>0.04787837713956833</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.01518404949456453</v>
+        <v>0.05121799558401108</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.01790427416563034</v>
+        <v>0.02508397400379181</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.02329953759908676</v>
+        <v>0.08355890959501266</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.01425187382847071</v>
+        <v>0.03372684121131897</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.003499445039778948</v>
+        <v>0.1057003885507584</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.002273515798151493</v>
+        <v>0.03244867920875549</v>
       </c>
     </row>
     <row r="14">
@@ -8396,1709 +8396,1709 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.004003946203738451</v>
+        <v>0.2582460343837738</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01325512025505304</v>
+        <v>0.4561197757720947</v>
       </c>
       <c r="C15" t="n">
-        <v>0.008434206247329712</v>
+        <v>0.3228208124637604</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002566887997090816</v>
+        <v>0.4968783855438232</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01370459888130426</v>
+        <v>0.6802057027816772</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001435591140761971</v>
+        <v>0.169719859957695</v>
       </c>
       <c r="G15" t="n">
-        <v>0.007172403857111931</v>
+        <v>0.2013800442218781</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001161716063506901</v>
+        <v>0.0988321527838707</v>
       </c>
       <c r="I15" t="n">
-        <v>0.004386952612549067</v>
+        <v>0.05907750129699707</v>
       </c>
       <c r="J15" t="n">
-        <v>0.003090270794928074</v>
+        <v>0.07533124834299088</v>
       </c>
       <c r="K15" t="n">
-        <v>0.009386987425386906</v>
+        <v>0.6021420359611511</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00601956807076931</v>
+        <v>0.1448782384395599</v>
       </c>
       <c r="M15" t="n">
-        <v>0.00768424104899168</v>
+        <v>0.4968478083610535</v>
       </c>
       <c r="N15" t="n">
-        <v>0.02085842005908489</v>
+        <v>0.7494121789932251</v>
       </c>
       <c r="O15" t="n">
-        <v>0.004197305999696255</v>
+        <v>0.1712128520011902</v>
       </c>
       <c r="P15" t="n">
-        <v>0.005643626675009727</v>
+        <v>0.05041107162833214</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.002567792776972055</v>
+        <v>0.3823444843292236</v>
       </c>
       <c r="R15" t="n">
-        <v>0.001281976932659745</v>
+        <v>0.1231871321797371</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0008258412126451731</v>
+        <v>0.1821669340133667</v>
       </c>
       <c r="T15" t="n">
-        <v>0.004371552262455225</v>
+        <v>0.3256103098392487</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0002225235803052783</v>
+        <v>0.2371446192264557</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0005637770518660545</v>
+        <v>0.09448819607496262</v>
       </c>
       <c r="W15" t="n">
-        <v>0.003596107242628932</v>
+        <v>0.2251921445131302</v>
       </c>
       <c r="X15" t="n">
-        <v>0.002741827163845301</v>
+        <v>0.1130626648664474</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0008311188430525362</v>
+        <v>0.06082619726657867</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.0001321215531788766</v>
+        <v>0.06749844551086426</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.000150543957715854</v>
+        <v>0.03053704276680946</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.001102462643757463</v>
+        <v>0.08885420858860016</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.004910745657980442</v>
+        <v>0.2381131500005722</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.001992529723793268</v>
+        <v>0.3197126984596252</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.001118161133490503</v>
+        <v>0.04473217204213142</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.003104699775576591</v>
+        <v>0.09998134523630142</v>
       </c>
       <c r="AG15" t="n">
-        <v>7.491768337786198e-05</v>
+        <v>0.2250561416149139</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.001083793351426721</v>
+        <v>0.2021582424640656</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.002886256668716669</v>
+        <v>0.3100301325321198</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.003331190440803766</v>
+        <v>0.126360222697258</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.0008844734984450042</v>
+        <v>0.2351817190647125</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.006409476045519114</v>
+        <v>0.4701434373855591</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.0004918174236081541</v>
+        <v>0.2023563832044601</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.001097520114853978</v>
+        <v>0.09936067461967468</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.001918227411806583</v>
+        <v>0.4648106694221497</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.003851904766634107</v>
+        <v>0.1240550577640533</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.002733056433498859</v>
+        <v>0.03830765932798386</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.003551610745489597</v>
+        <v>0.1992015540599823</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.00476709334179759</v>
+        <v>0.07721129059791565</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.006963322404772043</v>
+        <v>0.2839585542678833</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.01624748669564724</v>
+        <v>0.7791882157325745</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.005924713332206011</v>
+        <v>0.2968156039714813</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.005496436730027199</v>
+        <v>0.3113718330860138</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.004661369603127241</v>
+        <v>0.411391019821167</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.001747774425894022</v>
+        <v>0.02910785749554634</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.002747827209532261</v>
+        <v>0.006347782909870148</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.003487496636807919</v>
+        <v>0.2078655511140823</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.00258428743109107</v>
+        <v>0.090488001704216</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.002935535274446011</v>
+        <v>0.2191908210515976</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.001475266879424453</v>
+        <v>0.6707611083984375</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.00407017394900322</v>
+        <v>0.4928513765335083</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.005767678841948509</v>
+        <v>0.1994708180427551</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.01570729725062847</v>
+        <v>1.189187288284302</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.00361230131238699</v>
+        <v>0.3620936572551727</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.00338136195205152</v>
+        <v>0.03724281117320061</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.003456826554611325</v>
+        <v>0.2706025540828705</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.002036446705460548</v>
+        <v>0.04970260336995125</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.004700642079114914</v>
+        <v>0.1479710936546326</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.004353960510343313</v>
+        <v>0.05118495970964432</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.002584083471447229</v>
+        <v>0.01459983363747597</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.003576856572180986</v>
+        <v>0.1893805116415024</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.01380861550569534</v>
+        <v>0.09671500325202942</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.00219031423330307</v>
+        <v>0.2797394394874573</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.003784516360610723</v>
+        <v>0.04480097442865372</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.006549211218953133</v>
+        <v>0.04494243487715721</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.002338206628337502</v>
+        <v>0.09210009127855301</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.003889832645654678</v>
+        <v>0.2401264160871506</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.006610734853893518</v>
+        <v>1.065578699111938</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.008021049201488495</v>
+        <v>0.3326823115348816</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.0009347657323814929</v>
+        <v>0.09949225187301636</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.002062897197902203</v>
+        <v>0.1705870181322098</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.0003236450429540128</v>
+        <v>0.1795892119407654</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.004756541922688484</v>
+        <v>0.1325348019599915</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.0002477657981216908</v>
+        <v>0.01469624042510986</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.001018004142679274</v>
+        <v>0.03385961428284645</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.000732834218069911</v>
+        <v>0.2982345223426819</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.003249798901379108</v>
+        <v>0.2997071444988251</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.0003211336152162403</v>
+        <v>0.04785870388150215</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.002355359960347414</v>
+        <v>0.1513054370880127</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.00241000228561461</v>
+        <v>0.104531355202198</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.0001414652069797739</v>
+        <v>0.01912129297852516</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.0002478463866282254</v>
+        <v>0.006928849034011364</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.0005553641822189093</v>
+        <v>0.06650111079216003</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.001283129560761154</v>
+        <v>0.08924327790737152</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.006886087357997894</v>
+        <v>0.06924298405647278</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.002744710305705667</v>
+        <v>0.4345195889472961</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.00258698919788003</v>
+        <v>0.1014911681413651</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.0002505695447325706</v>
+        <v>0.1492496132850647</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.001414319733157754</v>
+        <v>0.279900461435318</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.001977395499125123</v>
+        <v>0.3622385859489441</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.0001014245208352804</v>
+        <v>0.1447893977165222</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.0002577505656518042</v>
+        <v>0.2140684723854065</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.002401183359324932</v>
+        <v>0.01062843576073647</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.000924036605283618</v>
+        <v>0.2311141490936279</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.002070571528747678</v>
+        <v>0.2428658008575439</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.0001187916495837271</v>
+        <v>0.09127490967512131</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.001599554205313325</v>
+        <v>0.07139638811349869</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.002147336723282933</v>
+        <v>0.1083027571439743</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.0004416762094479054</v>
+        <v>0.02253693155944347</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.0004822404007427394</v>
+        <v>0.03052864968776703</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.763146767392755e-06</v>
+        <v>0.1116744875907898</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.001715810503810644</v>
+        <v>0.1192055642604828</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.001995375147089362</v>
+        <v>0.04705186188220978</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.009432845748960972</v>
+        <v>0.4361686110496521</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.0001432411663699895</v>
+        <v>0.01476189494132996</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.001346235978417099</v>
+        <v>0.1286679059267044</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.002908368362113833</v>
+        <v>0.007270850241184235</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.0002979370765388012</v>
+        <v>0.09629824757575989</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.007168478332459927</v>
+        <v>0.2151883542537689</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.003095888067036867</v>
+        <v>0.2365776002407074</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.002925826702266932</v>
+        <v>0.3908824920654297</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.003692056052386761</v>
+        <v>0.2894287705421448</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.003259495832026005</v>
+        <v>0.06057509034872055</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.001181135070510209</v>
+        <v>0.126981794834137</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.001881300006061792</v>
+        <v>0.013639772310853</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.001050698920153081</v>
+        <v>0.3227346837520599</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.003414023900404572</v>
+        <v>0.0506172738969326</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.005586978979408741</v>
+        <v>0.04307816922664642</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.004576035775244236</v>
+        <v>0.06892626732587814</v>
       </c>
       <c r="DV15" t="n">
-        <v>5.358061753213406e-05</v>
+        <v>0.07719174027442932</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.004510171245783567</v>
+        <v>0.2061345428228378</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.001332470215857029</v>
+        <v>0.417772650718689</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.001056349254213274</v>
+        <v>0.1150315552949905</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.003080181311815977</v>
+        <v>0.2401955127716064</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.001942923991009593</v>
+        <v>0.3864512145519257</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.004594040103256702</v>
+        <v>0.08247728645801544</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.001052009407430887</v>
+        <v>0.006964722648262978</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.0008696184959262609</v>
+        <v>0.01839102245867252</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.00108338997233659</v>
+        <v>0.3184034824371338</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.0001833860296756029</v>
+        <v>0.05370804667472839</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.0003831417707260698</v>
+        <v>0.0984991192817688</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.0008502457640133798</v>
+        <v>0.03263826295733452</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.003087922930717468</v>
+        <v>0.09623302519321442</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.003207190195098519</v>
+        <v>0.04291226342320442</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.0008775186724960804</v>
+        <v>0.00833397638052702</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.003969674464315176</v>
+        <v>0.003732690587639809</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.001611311687156558</v>
+        <v>0.1414718478918076</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.002557615982368588</v>
+        <v>0.0009947642683982849</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.00203823740594089</v>
+        <v>0.1823637783527374</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.0004765833728015423</v>
+        <v>0.3188503384590149</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.003696304280310869</v>
+        <v>0.1994322538375854</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.0008713497663848102</v>
+        <v>0.005232909694314003</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.001156981335952878</v>
+        <v>0.1559674888849258</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.000954094750341028</v>
+        <v>0.01946649327874184</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.005116474814713001</v>
+        <v>0.09261246770620346</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.002599148778244853</v>
+        <v>0.1257190406322479</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.003508592722937465</v>
+        <v>0.1445501446723938</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.0007128564757294953</v>
+        <v>0.3268879055976868</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.002186290686950088</v>
+        <v>0.2752353549003601</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.0001140915119322017</v>
+        <v>0.042939443141222</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.001953751780092716</v>
+        <v>0.1176329851150513</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.003118320135399699</v>
+        <v>0.089785136282444</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.000156059511937201</v>
+        <v>0.009524230845272541</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.0009135653963312507</v>
+        <v>0.002832702361047268</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.0003870687505695969</v>
+        <v>0.1189239472150803</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.0002587545313872397</v>
+        <v>0.113284096121788</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.005177861079573631</v>
+        <v>0.04456100612878799</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.003343183314427733</v>
+        <v>0.1501155346632004</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.002324374858289957</v>
+        <v>0.3418464958667755</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.0001015667803585529</v>
+        <v>0.1251151710748672</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.002370509784668684</v>
+        <v>0.2518282234668732</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.0005856056232005358</v>
+        <v>0.1887829452753067</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.002411041874438524</v>
+        <v>0.04379631206393242</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.004131346940994263</v>
+        <v>0.1233243718743324</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.002808234887197614</v>
+        <v>0.1970497518777847</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.002021112479269505</v>
+        <v>0.1748460233211517</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.00367979658767581</v>
+        <v>0.2636253237724304</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.004286367911845446</v>
+        <v>0.4891775250434875</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.005957896821200848</v>
+        <v>0.295228511095047</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.00464492104947567</v>
+        <v>0.3808687031269073</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.001970507437363267</v>
+        <v>0.05418716371059418</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.0002553192898631096</v>
+        <v>0.1023418083786964</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.0053484165109694</v>
+        <v>0.01714455708861351</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.002292544115334749</v>
+        <v>0.1291778534650803</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.001771177630871534</v>
+        <v>0.2949701249599457</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.003346191719174385</v>
+        <v>0.3844901025295258</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.001315116882324219</v>
+        <v>0.07615071535110474</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.005957205314189196</v>
+        <v>0.01708481460809708</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.001958012813702226</v>
+        <v>0.01805825904011726</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.00587029941380024</v>
+        <v>0.2035445719957352</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.003620647825300694</v>
+        <v>0.005946912802755833</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.0001274090027436614</v>
+        <v>0.03290092572569847</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.001357917441055179</v>
+        <v>0.05975322425365448</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9.323027188656852e-05</v>
+        <v>4.190028994344175e-05</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0005014297785237432</v>
+        <v>0.0003689996083267033</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0002188557991757989</v>
+        <v>5.085988232167438e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>9.54038041527383e-05</v>
+        <v>9.635708556743339e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0001724394678603858</v>
+        <v>0.0001648095203563571</v>
       </c>
       <c r="F16" t="n">
-        <v>2.298292383784428e-05</v>
+        <v>4.793639527633786e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>7.057460607029498e-06</v>
+        <v>4.443792931851931e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0001115867707994767</v>
+        <v>4.597254155669361e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>8.566008546040393e-06</v>
+        <v>7.360824383795261e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>1.828553649829701e-05</v>
+        <v>8.858014189172536e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0003584201622288674</v>
+        <v>0.0005439812666736543</v>
       </c>
       <c r="L16" t="n">
-        <v>9.662585944170132e-05</v>
+        <v>8.605173206888139e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>9.883846360025927e-05</v>
+        <v>0.0001590579486219212</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0002459270472172648</v>
+        <v>0.0002755564928520471</v>
       </c>
       <c r="O16" t="n">
-        <v>1.099298424378503e-05</v>
+        <v>6.592358113266528e-05</v>
       </c>
       <c r="P16" t="n">
-        <v>1.238628465216607e-05</v>
+        <v>3.978527820436284e-05</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.766259240161162e-05</v>
+        <v>0.0002175456611439586</v>
       </c>
       <c r="R16" t="n">
-        <v>3.674590698210523e-05</v>
+        <v>0.0001319634029641747</v>
       </c>
       <c r="S16" t="n">
-        <v>1.994193917198572e-05</v>
+        <v>3.30041439156048e-05</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0001076500193448737</v>
+        <v>9.817711543291807e-05</v>
       </c>
       <c r="U16" t="n">
-        <v>5.2998755563749e-05</v>
+        <v>7.940591603983194e-05</v>
       </c>
       <c r="V16" t="n">
-        <v>1.317451824434102e-05</v>
+        <v>0.0001304495090153068</v>
       </c>
       <c r="W16" t="n">
-        <v>2.054004653473385e-06</v>
+        <v>8.755188173381612e-05</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0001696559193078429</v>
+        <v>1.583607627253514e-06</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.123026181128807e-05</v>
+        <v>3.731017204700038e-05</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.910286851460114e-05</v>
+        <v>1.643850919208489e-05</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.715029722821782e-06</v>
+        <v>1.235006038768915e-06</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.702208000002429e-06</v>
+        <v>2.036643672909122e-05</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0001267592451767996</v>
+        <v>5.025455902796239e-05</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.832575723412447e-05</v>
+        <v>1.975053783098701e-05</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.569281787145883e-05</v>
+        <v>4.429188993526623e-05</v>
       </c>
       <c r="AF16" t="n">
-        <v>9.153171413345262e-05</v>
+        <v>0.0001448460971005261</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.333278487436473e-05</v>
+        <v>6.765581201761961e-05</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.684400169528089e-05</v>
+        <v>3.960179310524836e-05</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.529953806311823e-05</v>
+        <v>0.0001270667999051511</v>
       </c>
       <c r="AJ16" t="n">
-        <v>9.58104010351235e-07</v>
+        <v>1.894415254355408e-05</v>
       </c>
       <c r="AK16" t="n">
-        <v>4.523250754573382e-05</v>
+        <v>2.479123031662311e-05</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0001372768601868302</v>
+        <v>3.879850555676967e-05</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.982785033760592e-05</v>
+        <v>4.794071355718188e-05</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.81492305273423e-06</v>
+        <v>6.37869889033027e-05</v>
       </c>
       <c r="AO16" t="n">
-        <v>6.193308217916638e-05</v>
+        <v>7.099007780198008e-05</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.030417742091231e-05</v>
+        <v>3.650685903267004e-05</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.931925180542748e-05</v>
+        <v>5.013540430809371e-05</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.70587172760861e-05</v>
+        <v>0.000138116258312948</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.692088961950503e-05</v>
+        <v>3.93106383853592e-05</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.452905654441565e-05</v>
+        <v>3.926824138034135e-05</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.0005237510777078569</v>
+        <v>0.0005260883481241763</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.0001001268465188332</v>
+        <v>5.032222543377429e-05</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.365525076835183e-05</v>
+        <v>3.761646439670585e-05</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.517833829391748e-05</v>
+        <v>4.914657256449573e-05</v>
       </c>
       <c r="AY16" t="n">
-        <v>2.058880090771709e-05</v>
+        <v>1.315088593401015e-05</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.156328602926806e-05</v>
+        <v>2.821843281708425e-06</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.0001001488999463618</v>
+        <v>4.920084393233992e-05</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0001398106833221391</v>
+        <v>5.455961218103766e-05</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.78305108420318e-05</v>
+        <v>0.0001403209171257913</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.219916859758087e-05</v>
+        <v>8.068988972809166e-05</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.8904271251522e-05</v>
+        <v>2.155076435883529e-05</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.352134652028326e-05</v>
+        <v>7.866251689847559e-05</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.0002926987654063851</v>
+        <v>9.692150342743844e-05</v>
       </c>
       <c r="BH16" t="n">
-        <v>6.666933768428862e-05</v>
+        <v>1.879368937807158e-05</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.427879215043504e-05</v>
+        <v>3.880412623402663e-05</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.968401738849934e-05</v>
+        <v>7.606644794577733e-05</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.348040991113521e-05</v>
+        <v>2.956417120003607e-05</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.0001537942735012621</v>
+        <v>1.989594056794886e-05</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.000126713581266813</v>
+        <v>0.0001993199257412925</v>
       </c>
       <c r="BN16" t="n">
-        <v>6.463954196078703e-05</v>
+        <v>3.831402136711404e-05</v>
       </c>
       <c r="BO16" t="n">
-        <v>7.687690231250599e-05</v>
+        <v>3.831141293630935e-05</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.0002045948785962537</v>
+        <v>0.0002177015121560544</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.07917684444692e-05</v>
+        <v>0.000113555790449027</v>
       </c>
       <c r="BR16" t="n">
-        <v>2.719259282457642e-05</v>
+        <v>0.0001857443858170882</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.0001091774247470312</v>
+        <v>3.733544144779444e-05</v>
       </c>
       <c r="BT16" t="n">
-        <v>1.502481973147951e-05</v>
+        <v>1.967504249478225e-05</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.213604890741408e-05</v>
+        <v>0.0001197027595480904</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.0002543159062042832</v>
+        <v>0.0003464990586508065</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.0001535190676804632</v>
+        <v>8.2797123468481e-05</v>
       </c>
       <c r="BX16" t="n">
-        <v>4.764140612678602e-05</v>
+        <v>0.0001111831807065755</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.0001178806705866009</v>
+        <v>5.026922372053377e-05</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0001370606478303671</v>
+        <v>4.388304660096765e-06</v>
       </c>
       <c r="CA16" t="n">
-        <v>7.572553295176476e-05</v>
+        <v>9.077626600628719e-05</v>
       </c>
       <c r="CB16" t="n">
-        <v>1.557512223371305e-05</v>
+        <v>1.098011671274435e-05</v>
       </c>
       <c r="CC16" t="n">
-        <v>9.810502524487674e-05</v>
+        <v>4.335217090556398e-05</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.470619776635431e-05</v>
+        <v>8.044205969781615e-06</v>
       </c>
       <c r="CE16" t="n">
-        <v>9.293587936554104e-05</v>
+        <v>0.0001261568686459213</v>
       </c>
       <c r="CF16" t="n">
-        <v>1.879931551229674e-05</v>
+        <v>2.87719230982475e-05</v>
       </c>
       <c r="CG16" t="n">
-        <v>5.397172571974806e-05</v>
+        <v>2.60673896264052e-05</v>
       </c>
       <c r="CH16" t="n">
-        <v>5.721504294342594e-06</v>
+        <v>4.839248504140414e-05</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.66116694547236e-05</v>
+        <v>2.524246883695014e-05</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.816749110934325e-05</v>
+        <v>1.544468250358477e-05</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.676724241406191e-05</v>
+        <v>9.52404661802575e-06</v>
       </c>
       <c r="CL16" t="n">
-        <v>8.863403309078421e-06</v>
+        <v>3.159471089020371e-05</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.0001519485813332722</v>
+        <v>0.0001239910343429074</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.0001480045611970127</v>
+        <v>0.0003309369785711169</v>
       </c>
       <c r="CO16" t="n">
-        <v>4.952793460688554e-05</v>
+        <v>3.932550316676497e-05</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.460586281609721e-05</v>
+        <v>0.0002159313589800149</v>
       </c>
       <c r="CQ16" t="n">
-        <v>8.937879465520382e-05</v>
+        <v>3.494763950584456e-05</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.838878779381048e-05</v>
+        <v>6.200330972205848e-06</v>
       </c>
       <c r="CS16" t="n">
-        <v>1.058774432749487e-05</v>
+        <v>2.174127439502627e-05</v>
       </c>
       <c r="CT16" t="n">
-        <v>5.970973234070698e-06</v>
+        <v>1.845180668169633e-05</v>
       </c>
       <c r="CU16" t="n">
-        <v>6.836726242909208e-05</v>
+        <v>1.31209526443854e-05</v>
       </c>
       <c r="CV16" t="n">
-        <v>4.241502756485716e-05</v>
+        <v>4.575600905809551e-05</v>
       </c>
       <c r="CW16" t="n">
-        <v>6.79586228216067e-05</v>
+        <v>0.0001200950646307319</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.354885262117023e-05</v>
+        <v>2.655201751622371e-05</v>
       </c>
       <c r="CY16" t="n">
-        <v>5.954355219728313e-05</v>
+        <v>5.231357863522135e-05</v>
       </c>
       <c r="CZ16" t="n">
-        <v>1.263500234927051e-05</v>
+        <v>2.099058838211931e-05</v>
       </c>
       <c r="DA16" t="n">
-        <v>3.591455606510863e-05</v>
+        <v>1.68276146723656e-05</v>
       </c>
       <c r="DB16" t="n">
-        <v>2.88328665192239e-05</v>
+        <v>4.655898919736501e-07</v>
       </c>
       <c r="DC16" t="n">
-        <v>8.549286576453596e-06</v>
+        <v>1.585173231433146e-05</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.207775833085179e-05</v>
+        <v>2.141280128853396e-05</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.000112738081952557</v>
+        <v>3.817962351604365e-05</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.000168211234267801</v>
+        <v>0.0001334686967311427</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.101783684338443e-05</v>
+        <v>4.45283149019815e-06</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0001619420218048617</v>
+        <v>1.190646253235172e-05</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.0001232728391187266</v>
+        <v>5.690766920452006e-05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>5.294664879329503e-05</v>
+        <v>7.72154307924211e-05</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.414010567823425e-05</v>
+        <v>1.71180690813344e-05</v>
       </c>
       <c r="DL16" t="n">
-        <v>2.022203079832252e-05</v>
+        <v>3.722053588717245e-05</v>
       </c>
       <c r="DM16" t="n">
-        <v>7.616123184561729e-05</v>
+        <v>1.604191129445098e-05</v>
       </c>
       <c r="DN16" t="n">
-        <v>7.335177360801026e-05</v>
+        <v>3.570010449038818e-05</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.180801857321057e-06</v>
+        <v>7.541465311078355e-05</v>
       </c>
       <c r="DP16" t="n">
-        <v>2.009029958571773e-05</v>
+        <v>1.043930751620792e-05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>2.568838681327179e-05</v>
+        <v>8.80662482813932e-05</v>
       </c>
       <c r="DR16" t="n">
-        <v>1.31688175315503e-05</v>
+        <v>3.654316969914362e-05</v>
       </c>
       <c r="DS16" t="n">
-        <v>1.213269752042834e-05</v>
+        <v>6.601512723136693e-05</v>
       </c>
       <c r="DT16" t="n">
-        <v>1.802886799850967e-05</v>
+        <v>8.097737918433268e-06</v>
       </c>
       <c r="DU16" t="n">
-        <v>6.217150075826794e-05</v>
+        <v>4.192049527773634e-05</v>
       </c>
       <c r="DV16" t="n">
-        <v>3.653740350273438e-05</v>
+        <v>5.409129698819015e-06</v>
       </c>
       <c r="DW16" t="n">
-        <v>6.447864143410698e-05</v>
+        <v>0.0001450575655326247</v>
       </c>
       <c r="DX16" t="n">
-        <v>2.260218025185168e-06</v>
+        <v>7.786036439938471e-05</v>
       </c>
       <c r="DY16" t="n">
-        <v>1.490060185460607e-05</v>
+        <v>2.140399192285258e-05</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.573493424686603e-05</v>
+        <v>2.371889877395006e-06</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.0001034509186865762</v>
+        <v>5.138814231031574e-05</v>
       </c>
       <c r="EB16" t="n">
-        <v>2.757771108008455e-05</v>
+        <v>4.657339377445169e-05</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.969791941926815e-05</v>
+        <v>5.918982424191199e-07</v>
       </c>
       <c r="ED16" t="n">
-        <v>3.800365448114462e-05</v>
+        <v>2.92025815724628e-05</v>
       </c>
       <c r="EE16" t="n">
-        <v>3.698281943798065e-05</v>
+        <v>2.597501406853553e-05</v>
       </c>
       <c r="EF16" t="n">
-        <v>1.342255745839793e-05</v>
+        <v>8.319670450873673e-05</v>
       </c>
       <c r="EG16" t="n">
-        <v>3.889292565872893e-05</v>
+        <v>5.039187817601487e-05</v>
       </c>
       <c r="EH16" t="n">
-        <v>4.040941803395981e-07</v>
+        <v>2.876908183679916e-05</v>
       </c>
       <c r="EI16" t="n">
-        <v>9.015738760353997e-05</v>
+        <v>1.317344140261412e-05</v>
       </c>
       <c r="EJ16" t="n">
-        <v>4.073761738254689e-05</v>
+        <v>7.774665391480085e-06</v>
       </c>
       <c r="EK16" t="n">
-        <v>3.273994298069738e-05</v>
+        <v>4.786200588569045e-05</v>
       </c>
       <c r="EL16" t="n">
-        <v>3.962309347116388e-05</v>
+        <v>2.18351669900585e-06</v>
       </c>
       <c r="EM16" t="n">
-        <v>2.079080513794906e-05</v>
+        <v>3.245076368330047e-05</v>
       </c>
       <c r="EN16" t="n">
-        <v>1.618014721316285e-05</v>
+        <v>5.292648347676732e-05</v>
       </c>
       <c r="EO16" t="n">
-        <v>3.012984416272957e-05</v>
+        <v>4.691139474743977e-05</v>
       </c>
       <c r="EP16" t="n">
-        <v>5.439189408207312e-05</v>
+        <v>4.062057269038633e-05</v>
       </c>
       <c r="EQ16" t="n">
-        <v>3.049645238206722e-05</v>
+        <v>3.060450035263784e-05</v>
       </c>
       <c r="ER16" t="n">
-        <v>2.785350625345018e-05</v>
+        <v>3.444102185312659e-05</v>
       </c>
       <c r="ES16" t="n">
-        <v>2.326599314983469e-06</v>
+        <v>7.666330202482641e-05</v>
       </c>
       <c r="ET16" t="n">
-        <v>7.80811024014838e-05</v>
+        <v>2.552993828430772e-05</v>
       </c>
       <c r="EU16" t="n">
-        <v>7.744415052002296e-05</v>
+        <v>2.025963112828322e-05</v>
       </c>
       <c r="EV16" t="n">
-        <v>8.302494825329632e-05</v>
+        <v>4.120754965697415e-06</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.0001519248471595347</v>
+        <v>4.866259041591547e-05</v>
       </c>
       <c r="EX16" t="n">
-        <v>3.546230800566263e-05</v>
+        <v>1.91226845345227e-05</v>
       </c>
       <c r="EY16" t="n">
-        <v>8.243061893153936e-05</v>
+        <v>0.0001565620477776974</v>
       </c>
       <c r="EZ16" t="n">
-        <v>2.933533323812298e-05</v>
+        <v>1.697308471193537e-05</v>
       </c>
       <c r="FA16" t="n">
-        <v>6.476626731455326e-05</v>
+        <v>5.267287633614615e-05</v>
       </c>
       <c r="FB16" t="n">
-        <v>9.715026862977538e-07</v>
+        <v>6.599503649340477e-06</v>
       </c>
       <c r="FC16" t="n">
-        <v>3.144017682643607e-05</v>
+        <v>2.057627716567367e-05</v>
       </c>
       <c r="FD16" t="n">
-        <v>3.973553248215467e-05</v>
+        <v>2.427140316285659e-05</v>
       </c>
       <c r="FE16" t="n">
-        <v>1.069114387064474e-05</v>
+        <v>7.498505965486402e-06</v>
       </c>
       <c r="FF16" t="n">
-        <v>1.075071395462146e-05</v>
+        <v>3.251835732953623e-05</v>
       </c>
       <c r="FG16" t="n">
-        <v>9.110032260650769e-05</v>
+        <v>3.480688246781938e-05</v>
       </c>
       <c r="FH16" t="n">
-        <v>7.925086538307369e-05</v>
+        <v>7.882203499320894e-05</v>
       </c>
       <c r="FI16" t="n">
-        <v>3.401738649699837e-05</v>
+        <v>2.156144728360232e-05</v>
       </c>
       <c r="FJ16" t="n">
-        <v>1.284320569538977e-05</v>
+        <v>0.0001329931546933949</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.0001030725470627658</v>
+        <v>6.04261840635445e-05</v>
       </c>
       <c r="FL16" t="n">
-        <v>8.035094651859254e-06</v>
+        <v>2.947922621387988e-05</v>
       </c>
       <c r="FM16" t="n">
-        <v>2.100733399856836e-05</v>
+        <v>5.283033169689588e-05</v>
       </c>
       <c r="FN16" t="n">
-        <v>3.420557550271042e-05</v>
+        <v>1.94326821656432e-05</v>
       </c>
       <c r="FO16" t="n">
-        <v>8.714738942217082e-05</v>
+        <v>4.05870086979121e-05</v>
       </c>
       <c r="FP16" t="n">
-        <v>3.448798815952614e-05</v>
+        <v>2.73388341156533e-05</v>
       </c>
       <c r="FQ16" t="n">
-        <v>5.155664985068142e-05</v>
+        <v>5.390209116740152e-05</v>
       </c>
       <c r="FR16" t="n">
-        <v>7.18432929716073e-05</v>
+        <v>8.900638931663707e-06</v>
       </c>
       <c r="FS16" t="n">
-        <v>8.278097811853513e-05</v>
+        <v>0.000163935765158385</v>
       </c>
       <c r="FT16" t="n">
-        <v>1.068321762431879e-05</v>
+        <v>0.0003076163993682712</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.0001131391909439117</v>
+        <v>5.606408740277402e-05</v>
       </c>
       <c r="FV16" t="n">
-        <v>6.147133535705507e-05</v>
+        <v>3.453301178524271e-05</v>
       </c>
       <c r="FW16" t="n">
-        <v>2.626972218422452e-06</v>
+        <v>6.194949673954397e-05</v>
       </c>
       <c r="FX16" t="n">
-        <v>6.020910586812533e-05</v>
+        <v>1.776928183971904e-05</v>
       </c>
       <c r="FY16" t="n">
-        <v>6.448908243328333e-05</v>
+        <v>7.094616739777848e-05</v>
       </c>
       <c r="FZ16" t="n">
-        <v>8.37944753584452e-05</v>
+        <v>0.0001059216883732006</v>
       </c>
       <c r="GA16" t="n">
-        <v>3.364937947480939e-05</v>
+        <v>6.071455209166743e-05</v>
       </c>
       <c r="GB16" t="n">
-        <v>4.389382229419425e-05</v>
+        <v>2.898564343922772e-05</v>
       </c>
       <c r="GC16" t="n">
-        <v>7.316612027352676e-05</v>
+        <v>2.7940523068537e-05</v>
       </c>
       <c r="GD16" t="n">
-        <v>9.997636516345665e-05</v>
+        <v>7.683562580496073e-05</v>
       </c>
       <c r="GE16" t="n">
-        <v>8.999829879030585e-05</v>
+        <v>7.780922169331461e-05</v>
       </c>
       <c r="GF16" t="n">
-        <v>5.559751662076451e-05</v>
+        <v>0.0001085721960407682</v>
       </c>
       <c r="GG16" t="n">
-        <v>3.019566247530747e-05</v>
+        <v>2.289720032422338e-05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.0008505323203280568</v>
+        <v>0.02186999842524529</v>
       </c>
       <c r="B17" t="n">
-        <v>0.002843304304406047</v>
+        <v>0.02547555044293404</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0004335507692303509</v>
+        <v>0.007748068310320377</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0005595341790467501</v>
+        <v>0.009913464076817036</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0001836955052567646</v>
+        <v>0.01932311803102493</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00130123645067215</v>
+        <v>0.01222596876323223</v>
       </c>
       <c r="G17" t="n">
-        <v>4.769855877384543e-06</v>
+        <v>0.007557359524071217</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0005482171545736492</v>
+        <v>0.001049031037837267</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0001459946215618402</v>
+        <v>0.003354378510266542</v>
       </c>
       <c r="J17" t="n">
-        <v>0.000102009333204478</v>
+        <v>0.01147111132740974</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001710486831143498</v>
+        <v>0.04998951032757759</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0008099338156171143</v>
+        <v>0.006508979015052319</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0006558189052157104</v>
+        <v>0.01113205216825008</v>
       </c>
       <c r="N17" t="n">
-        <v>0.00106242869514972</v>
+        <v>0.02787100896239281</v>
       </c>
       <c r="O17" t="n">
-        <v>0.001074263593181968</v>
+        <v>0.006211698986589909</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0002131786750396714</v>
+        <v>0.008051151409745216</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.001764485496096313</v>
+        <v>0.02217353694140911</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0001899948401842266</v>
+        <v>0.01140887662768364</v>
       </c>
       <c r="S17" t="n">
-        <v>2.055658114841208e-05</v>
+        <v>0.003907484468072653</v>
       </c>
       <c r="T17" t="n">
-        <v>0.00054036860819906</v>
+        <v>0.006916739977896214</v>
       </c>
       <c r="U17" t="n">
-        <v>0.000784547533839941</v>
+        <v>0.0004218791727907956</v>
       </c>
       <c r="V17" t="n">
-        <v>7.536180783063173e-05</v>
+        <v>0.0007351901149377227</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0003536635776981711</v>
+        <v>0.005259048193693161</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0008458857191726565</v>
+        <v>0.004800098016858101</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.0002937891113106161</v>
+        <v>0.002092174720019102</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0002231291146017611</v>
+        <v>6.611039862036705e-05</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0001628676109248772</v>
+        <v>8.469464955851436e-05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0001309512590523809</v>
+        <v>0.0001362767070531845</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0008856215863488615</v>
+        <v>0.002628934103995562</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0005086867022328079</v>
+        <v>0.003152574878185987</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0004700322169810534</v>
+        <v>0.007526691537350416</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0005019218078814447</v>
+        <v>0.01065862644463778</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0001628994941711426</v>
+        <v>0.0006060193991288543</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.0008253748528659344</v>
+        <v>0.001769131049513817</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.0006980552570894361</v>
+        <v>0.01018057391047478</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4.21231088694185e-05</v>
+        <v>0.001787202432751656</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0004867812676820904</v>
+        <v>0.006367035210132599</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.0006674053147435188</v>
+        <v>0.005763212218880653</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.000118201453005895</v>
+        <v>0.00637135561555624</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.0001021297066472471</v>
+        <v>0.001155593665316701</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.0002377853234065697</v>
+        <v>0.006012086290866137</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.0007539290236309171</v>
+        <v>0.006472098175436258</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.0006081056199036539</v>
+        <v>0.005019763484597206</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.0004932766896672547</v>
+        <v>0.01040368899703026</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.0002360700309509411</v>
+        <v>0.001380533678457141</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.00053895462770015</v>
+        <v>0.001455181511119008</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.003804495092481375</v>
+        <v>0.04454609751701355</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.0003262669779360294</v>
+        <v>0.009539754129946232</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.0006100634927861392</v>
+        <v>0.00630608107894659</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.0008643987239338458</v>
+        <v>0.00014801713405177</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.0003572950081434101</v>
+        <v>0.001124367583543062</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.0003722329856827855</v>
+        <v>0.0007062794174998999</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.0004596968647092581</v>
+        <v>0.002799592912197113</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.0006475361878983676</v>
+        <v>0.0003543992061167955</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.0003033608663827181</v>
+        <v>0.01629694364964962</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.0007318822899833322</v>
+        <v>0.002723956946283579</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.0005353817250579596</v>
+        <v>0.01217777095735073</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.001205687178298831</v>
+        <v>0.004267373122274876</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.0006985719664953649</v>
+        <v>0.008399738930165768</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.001479849102906883</v>
+        <v>0.005010411143302917</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.0001336366985924542</v>
+        <v>0.0003248269204050303</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.001309941406361759</v>
+        <v>0.003659256035462022</v>
       </c>
       <c r="BK17" t="n">
-        <v>3.336419831612147e-05</v>
+        <v>0.0011290229158476</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.0001983356778509915</v>
+        <v>0.001684671966359019</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.002226844895631075</v>
+        <v>0.01519365329295397</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.0005207770154811442</v>
+        <v>0.004269314464181662</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.001019244780763984</v>
+        <v>0.00632343627512455</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.002088940469548106</v>
+        <v>0.01834659278392792</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.001089965924620628</v>
+        <v>0.01478682924062014</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.0002378632489126176</v>
+        <v>0.01228372100740671</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.001271849730983377</v>
+        <v>0.00145522621460259</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.0005001036915928125</v>
+        <v>0.0002316187601536512</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.0005397095228545368</v>
+        <v>0.007014761213213205</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.0016177719226107</v>
+        <v>0.03546378016471863</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.0003554804425220937</v>
+        <v>0.00871925987303257</v>
       </c>
       <c r="BX17" t="n">
-        <v>8.865914423950016e-06</v>
+        <v>0.003590760286897421</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.000208415454835631</v>
+        <v>0.001264489023014903</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.001270335982553661</v>
+        <v>0.00208261888474226</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.0008248433005064726</v>
+        <v>0.008126622065901756</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.0001764279440976679</v>
+        <v>0.005121717229485512</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.0001260311692021787</v>
+        <v>0.002839230699464679</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.0001185248984256759</v>
+        <v>0.005363990552723408</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.000428648287197575</v>
+        <v>0.007628541439771652</v>
       </c>
       <c r="CF17" t="n">
-        <v>6.78036012686789e-05</v>
+        <v>0.003970610443502665</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.000394594157114625</v>
+        <v>0.00253066816367209</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.0003345828736200929</v>
+        <v>0.003955793101340532</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.0003683910181280226</v>
+        <v>0.005297500640153885</v>
       </c>
       <c r="CJ17" t="n">
-        <v>8.979240374173969e-05</v>
+        <v>0.0005252984701655805</v>
       </c>
       <c r="CK17" t="n">
-        <v>8.337509643752128e-05</v>
+        <v>0.00201874109916389</v>
       </c>
       <c r="CL17" t="n">
-        <v>7.919032941572368e-05</v>
+        <v>0.002444198122248054</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.001016989466734231</v>
+        <v>0.01177801378071308</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.001943820039741695</v>
+        <v>0.03687803819775581</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.0001255898096133024</v>
+        <v>0.006357230246067047</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.0006152760470286012</v>
+        <v>0.009029598906636238</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.00136575975921005</v>
+        <v>0.003796612145379186</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.0003284615813754499</v>
+        <v>0.006841054651886225</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.0002130060456693172</v>
+        <v>0.007264880463480949</v>
       </c>
       <c r="CT17" t="n">
-        <v>9.048471838468686e-05</v>
+        <v>0.01009620446711779</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.0005521703860722482</v>
+        <v>0.003273387672379613</v>
       </c>
       <c r="CV17" t="n">
-        <v>3.636760084191337e-05</v>
+        <v>0.002468348015099764</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.0002990641514770687</v>
+        <v>0.008485965430736542</v>
       </c>
       <c r="CX17" t="n">
-        <v>3.400749119464308e-05</v>
+        <v>0.002665229607373476</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.0004323958128225058</v>
+        <v>0.001228570006787777</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.0001467148977098987</v>
+        <v>0.0006457122508436441</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.00064902997110039</v>
+        <v>0.003381933784112334</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.0001345511700492352</v>
+        <v>0.002441153395920992</v>
       </c>
       <c r="DC17" t="n">
-        <v>5.725699884351343e-05</v>
+        <v>0.001216292614117265</v>
       </c>
       <c r="DD17" t="n">
-        <v>5.181527740205638e-05</v>
+        <v>0.001883049961179495</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.001752988900989294</v>
+        <v>0.001848116982728243</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.002068067668005824</v>
+        <v>0.02545125409960747</v>
       </c>
       <c r="DG17" t="n">
-        <v>0.0007754967082291842</v>
+        <v>0.003561880206689239</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.001285947277210653</v>
+        <v>0.00839105062186718</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.001078109489753842</v>
+        <v>0.00146889709867537</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.0007399925962090492</v>
+        <v>0.004920975770801306</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.00173130095936358</v>
+        <v>0.0007582926191389561</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.0006031944649294019</v>
+        <v>0.005003585945814848</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.0003892921376973391</v>
+        <v>0.001195704331621528</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.0006848495686426759</v>
+        <v>0.00303687690757215</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.0007839691825211048</v>
+        <v>0.003132866229861975</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.0002630223461892456</v>
+        <v>0.005367103964090347</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.000127393810544163</v>
+        <v>0.0008964469889178872</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.0002974185917992145</v>
+        <v>0.005485334433615208</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.0002808726858347654</v>
+        <v>0.003479963634163141</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.0006212390726432204</v>
+        <v>0.0001221718266606331</v>
       </c>
       <c r="DU17" t="n">
-        <v>0.0004934776807203889</v>
+        <v>0.003182697575539351</v>
       </c>
       <c r="DV17" t="n">
-        <v>0.0001151808464783244</v>
+        <v>0.00221797195263207</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.0003236030752304941</v>
+        <v>0.00843815878033638</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.0004906771355308592</v>
+        <v>0.009280768223106861</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.0001460195198887959</v>
+        <v>0.006522397510707378</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.0008376942132599652</v>
+        <v>0.004799325950443745</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.0006476063863374293</v>
+        <v>0.005639989860355854</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.0009886116022244096</v>
+        <v>0.00436797272413969</v>
       </c>
       <c r="EC17" t="n">
-        <v>0.0005013816407881677</v>
+        <v>0.00119198311585933</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.0004486441030167043</v>
+        <v>0.001940542366355658</v>
       </c>
       <c r="EE17" t="n">
-        <v>0.0001150238604168408</v>
+        <v>0.002908738097175956</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.0002902068081311882</v>
+        <v>0.005812051706016064</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.0004246406315360218</v>
+        <v>0.0002585537731647491</v>
       </c>
       <c r="EH17" t="n">
-        <v>1.761327257554512e-05</v>
+        <v>0.005201330408453941</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.000441571872215718</v>
+        <v>0.001544137834571302</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.0001844052894739434</v>
+        <v>0.003037139307707548</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.0005844797706231475</v>
+        <v>0.008492262102663517</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.0003492832474876195</v>
+        <v>0.0009724709670990705</v>
       </c>
       <c r="EM17" t="n">
-        <v>0.0001637624227441847</v>
+        <v>0.002089647110551596</v>
       </c>
       <c r="EN17" t="n">
-        <v>7.782421016599983e-05</v>
+        <v>0.004535133950412273</v>
       </c>
       <c r="EO17" t="n">
-        <v>0.0003996954474132508</v>
+        <v>0.008153117261826992</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.0001398943568347022</v>
+        <v>0.000118607422336936</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.0001347508223261684</v>
+        <v>0.004160762298852205</v>
       </c>
       <c r="ER17" t="n">
-        <v>6.789007602492347e-05</v>
+        <v>0.004616651218384504</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.0003607983526308089</v>
+        <v>0.01204032171517611</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.0007015075534582138</v>
+        <v>0.0009635188616812229</v>
       </c>
       <c r="EU17" t="n">
-        <v>9.375947411172092e-05</v>
+        <v>0.005469315219670534</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.0004777990106958896</v>
+        <v>0.00144853675737977</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.0002766017278190702</v>
+        <v>0.002381274942308664</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.0001719754654914141</v>
+        <v>0.003534914460033178</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.0002865759888663888</v>
+        <v>0.01205554977059364</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.000181236260687001</v>
+        <v>0.002332399599254131</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.0003114977735094726</v>
+        <v>0.002464065561071038</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.0002843235270120203</v>
+        <v>0.0006512714899145067</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.0006284599076025188</v>
+        <v>0.005205765832215548</v>
       </c>
       <c r="FD17" t="n">
-        <v>9.312984184361994e-05</v>
+        <v>0.0001867139944806695</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.0002140489377779886</v>
+        <v>0.00215314538218081</v>
       </c>
       <c r="FF17" t="n">
-        <v>1.048707599693444e-05</v>
+        <v>0.003088202327489853</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.0006403629668056965</v>
+        <v>0.001848244573920965</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.000431936961831525</v>
+        <v>0.006236610002815723</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.0002324925153516233</v>
+        <v>0.002155028516426682</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.0001003763463813812</v>
+        <v>0.0029465202242136</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.0008442343678325415</v>
+        <v>0.01492093503475189</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.0006534696440212429</v>
+        <v>0.003951369784772396</v>
       </c>
       <c r="FM17" t="n">
-        <v>0.0001824360806494951</v>
+        <v>0.0008337012259289622</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.0002241824113298208</v>
+        <v>0.003149747382849455</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.0001455577003071085</v>
+        <v>0.0009935447014868259</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.0001033781154546887</v>
+        <v>0.005845697596669197</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.0002088439359795302</v>
+        <v>0.01572995074093342</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.0004384546482469887</v>
+        <v>0.005506261717528105</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.001283889869228005</v>
+        <v>0.004219597671180964</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.0005974715459160507</v>
+        <v>0.04794160276651382</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.0003727099974639714</v>
+        <v>0.0004873764701187611</v>
       </c>
       <c r="FV17" t="n">
-        <v>0.000358289573341608</v>
+        <v>0.0009851430077105761</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.0001450681156711653</v>
+        <v>0.0004681786522269249</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.0003975361178163439</v>
+        <v>0.001627461286261678</v>
       </c>
       <c r="FY17" t="n">
-        <v>2.687753294594586e-06</v>
+        <v>0.001248998800292611</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.001206466811709106</v>
+        <v>0.008479708805680275</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.0002359558711759746</v>
+        <v>0.00687215244397521</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.0009897089330479503</v>
+        <v>0.008417290635406971</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.0008747492101974785</v>
+        <v>0.005277472548186779</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.0005127352778799832</v>
+        <v>0.0160379521548748</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.000829711148981005</v>
+        <v>0.006704692263156176</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.0009746334981173277</v>
+        <v>0.003742989851161838</v>
       </c>
       <c r="GG17" t="n">
-        <v>6.88017244101502e-05</v>
+        <v>0.001032651285640895</v>
       </c>
     </row>
   </sheetData>
